--- a/docs/collections/kanok/metadata/data.xlsx
+++ b/docs/collections/kanok/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2416">
   <si>
     <t>資料名</t>
   </si>
@@ -6900,6 +6900,369 @@
   </si>
   <si>
     <t>0245</t>
+  </si>
+  <si>
+    <t>日記(明治31年4月~7月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ31</t>
+  </si>
+  <si>
+    <t>1898.4.1~7.22</t>
+  </si>
+  <si>
+    <t>45コマ</t>
+  </si>
+  <si>
+    <t>日記</t>
+  </si>
+  <si>
+    <t>日記08</t>
+  </si>
+  <si>
+    <t>五高教頭時代</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cc96c19e-326e-2e07-5dc6-11820a81a420.json</t>
+  </si>
+  <si>
+    <t>cc96c19e-326e-2e07-5dc6-11820a81a420</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/cc96c19e-326e-2e07-5dc6-11820a81a420</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cae4fd2e547b546758d82add1808e28af660576.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726490</t>
+  </si>
+  <si>
+    <t>0246</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cc96c19e-326e-2e07-5dc6-11820a81a420/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治31年7月~12月)</t>
+  </si>
+  <si>
+    <t>1898.7.23~12.4</t>
+  </si>
+  <si>
+    <t>54コマ</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4fb84f65-6f64-3852-2fca-520b41d96f28.json</t>
+  </si>
+  <si>
+    <t>4fb84f65-6f64-3852-2fca-520b41d96f28</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/4fb84f65-6f64-3852-2fca-520b41d96f28</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4e51d6bb457204b16c45204fc66981f72bcf2b08.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726491</t>
+  </si>
+  <si>
+    <t>0247</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4fb84f65-6f64-3852-2fca-520b41d96f28/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治32年1月~7月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ32</t>
+  </si>
+  <si>
+    <t>1899.1.22~7.31</t>
+  </si>
+  <si>
+    <t>105コマ</t>
+  </si>
+  <si>
+    <t>日記09</t>
+  </si>
+  <si>
+    <t>一高校長時代1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/284d2c19-08d7-a647-051f-a3a0a57f09df.json</t>
+  </si>
+  <si>
+    <t>284d2c19-08d7-a647-051f-a3a0a57f09df</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/284d2c19-08d7-a647-051f-a3a0a57f09df</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1889baab0424980dfd43217732aa9751ae903b21.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726492</t>
+  </si>
+  <si>
+    <t>0248</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/284d2c19-08d7-a647-051f-a3a0a57f09df/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治34年4月~5月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ34</t>
+  </si>
+  <si>
+    <t>1901.4.6~5.2</t>
+  </si>
+  <si>
+    <t>38コマ</t>
+  </si>
+  <si>
+    <t>日記10</t>
+  </si>
+  <si>
+    <t>一高校長時代2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ee3c9a98-a341-1266-30ee-26484bca854f.json</t>
+  </si>
+  <si>
+    <t>ee3c9a98-a341-1266-30ee-26484bca854f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/ee3c9a98-a341-1266-30ee-26484bca854f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2fc313f10b21aa8a9433994d42cd757205fcc1cc.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726493</t>
+  </si>
+  <si>
+    <t>0249</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ee3c9a98-a341-1266-30ee-26484bca854f/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治34年1月~5月)</t>
+  </si>
+  <si>
+    <t>1901.1.1~5.5</t>
+  </si>
+  <si>
+    <t>57コマ</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1d431059-3cef-9e24-17e6-eefa2c7fa05b.json</t>
+  </si>
+  <si>
+    <t>1d431059-3cef-9e24-17e6-eefa2c7fa05b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/1d431059-3cef-9e24-17e6-eefa2c7fa05b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1341a7ad2f79d295dc8ee1ac6429e78e44fa7701.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726494</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1d431059-3cef-9e24-17e6-eefa2c7fa05b/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治38年4月~39年3月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ38</t>
+  </si>
+  <si>
+    <t>1905.5.25~1906.3.29</t>
+  </si>
+  <si>
+    <t>29コマ</t>
+  </si>
+  <si>
+    <t>日記11</t>
+  </si>
+  <si>
+    <t>一高校長時代3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9417646e-362c-1884-3218-632bb8043503.json</t>
+  </si>
+  <si>
+    <t>9417646e-362c-1884-3218-632bb8043503</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9417646e-362c-1884-3218-632bb8043503</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a35d791c5dc941a572d73effb349a354289c88.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726495</t>
+  </si>
+  <si>
+    <t>0251</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9417646e-362c-1884-3218-632bb8043503/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治39年7月~11月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ39</t>
+  </si>
+  <si>
+    <t>1906.7.11~11.26</t>
+  </si>
+  <si>
+    <t>48コマ</t>
+  </si>
+  <si>
+    <t>日記12</t>
+  </si>
+  <si>
+    <t>京大文科学長時代1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5e77116c-4884-5ba2-511e-e7fa04cb8cc0.json</t>
+  </si>
+  <si>
+    <t>5e77116c-4884-5ba2-511e-e7fa04cb8cc0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/5e77116c-4884-5ba2-511e-e7fa04cb8cc0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1b6dbaa847b81cf96010dddb778dbe307bb523cb.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726496</t>
+  </si>
+  <si>
+    <t>0252</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5e77116c-4884-5ba2-511e-e7fa04cb8cc0/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治39年12月~40年4月)</t>
+  </si>
+  <si>
+    <t>1906.12.14~1907.4.2</t>
+  </si>
+  <si>
+    <t>28コマ</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/13544e9d-2555-1fbc-2f13-b4a115ca1001.json</t>
+  </si>
+  <si>
+    <t>13544e9d-2555-1fbc-2f13-b4a115ca1001</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/13544e9d-2555-1fbc-2f13-b4a115ca1001</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3902e809f3629c483dd2141e849ec262f2238dc8.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726497</t>
+  </si>
+  <si>
+    <t>0253</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/13544e9d-2555-1fbc-2f13-b4a115ca1001/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治40年2月~6月)</t>
+  </si>
+  <si>
+    <t>ニッキメイジ40</t>
+  </si>
+  <si>
+    <t>1907.2.12~6.21</t>
+  </si>
+  <si>
+    <t>52コマ</t>
+  </si>
+  <si>
+    <t>日記13</t>
+  </si>
+  <si>
+    <t>京大文科学長時代2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/60ddc98c-1470-5bb9-0e3c-986694f15d05.json</t>
+  </si>
+  <si>
+    <t>60ddc98c-1470-5bb9-0e3c-986694f15d05</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/60ddc98c-1470-5bb9-0e3c-986694f15d05</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/82e64328a1bd322962159c850201f16f2324239c.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726498</t>
+  </si>
+  <si>
+    <t>0254</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/60ddc98c-1470-5bb9-0e3c-986694f15d05/manifest</t>
+  </si>
+  <si>
+    <t>日記(明治40年7月~42年9月)</t>
+  </si>
+  <si>
+    <t>1907.7.25~1909.9.11</t>
+  </si>
+  <si>
+    <t>83コマ</t>
+  </si>
+  <si>
+    <t>日記14</t>
+  </si>
+  <si>
+    <t>京大文科学長時代3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c8447634-111b-8162-4c41-bf09167915d2.json</t>
+  </si>
+  <si>
+    <t>c8447634-111b-8162-4c41-bf09167915d2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/c8447634-111b-8162-4c41-bf09167915d2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dd01977d2db3bfd673afb75ec7b7901f19e9ece9.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/726499</t>
+  </si>
+  <si>
+    <t>0255</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c8447634-111b-8162-4c41-bf09167915d2/manifest</t>
   </si>
 </sst>
 </file>
@@ -7235,7 +7598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA247"/>
+  <dimension ref="A1:AA257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -7401,7 +7764,7 @@
         <v>51</v>
       </c>
       <c r="AA2" t="n">
-        <v>1148</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -23799,6 +24162,692 @@
         <v>0</v>
       </c>
     </row>
+    <row r="248" spans="1:27">
+      <c r="A248" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B248" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C248" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D248" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E248" t="s"/>
+      <c r="F248" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G248" t="s">
+        <v>2300</v>
+      </c>
+      <c r="H248" t="s">
+        <v>2301</v>
+      </c>
+      <c r="I248" t="s">
+        <v>2302</v>
+      </c>
+      <c r="J248" t="s">
+        <v>2303</v>
+      </c>
+      <c r="K248" t="s">
+        <v>60</v>
+      </c>
+      <c r="L248" t="s">
+        <v>2304</v>
+      </c>
+      <c r="M248" t="s">
+        <v>62</v>
+      </c>
+      <c r="N248" t="s">
+        <v>2305</v>
+      </c>
+      <c r="O248" t="s">
+        <v>2306</v>
+      </c>
+      <c r="P248" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>66</v>
+      </c>
+      <c r="R248" t="s"/>
+      <c r="S248" t="s">
+        <v>67</v>
+      </c>
+      <c r="T248" t="s">
+        <v>2307</v>
+      </c>
+      <c r="U248" t="s"/>
+      <c r="V248" t="s">
+        <v>2308</v>
+      </c>
+      <c r="W248" t="s"/>
+      <c r="X248" t="s"/>
+      <c r="Y248" t="s"/>
+      <c r="Z248" t="s"/>
+      <c r="AA248" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="249" spans="1:27">
+      <c r="A249" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B249" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C249" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D249" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E249" t="s"/>
+      <c r="F249" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G249" t="s">
+        <v>2300</v>
+      </c>
+      <c r="H249" t="s">
+        <v>2301</v>
+      </c>
+      <c r="I249" t="s">
+        <v>2312</v>
+      </c>
+      <c r="J249" t="s">
+        <v>2313</v>
+      </c>
+      <c r="K249" t="s">
+        <v>60</v>
+      </c>
+      <c r="L249" t="s">
+        <v>2314</v>
+      </c>
+      <c r="M249" t="s">
+        <v>62</v>
+      </c>
+      <c r="N249" t="s">
+        <v>2315</v>
+      </c>
+      <c r="O249" t="s">
+        <v>2316</v>
+      </c>
+      <c r="P249" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>66</v>
+      </c>
+      <c r="R249" t="s"/>
+      <c r="S249" t="s">
+        <v>67</v>
+      </c>
+      <c r="T249" t="s">
+        <v>2317</v>
+      </c>
+      <c r="U249" t="s"/>
+      <c r="V249" t="s">
+        <v>2318</v>
+      </c>
+      <c r="W249" t="s"/>
+      <c r="X249" t="s"/>
+      <c r="Y249" t="s"/>
+      <c r="Z249" t="s"/>
+      <c r="AA249" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="250" spans="1:27">
+      <c r="A250" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B250" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C250" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D250" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E250" t="s"/>
+      <c r="F250" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G250" t="s">
+        <v>2323</v>
+      </c>
+      <c r="H250" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I250" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J250" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K250" t="s">
+        <v>60</v>
+      </c>
+      <c r="L250" t="s">
+        <v>2327</v>
+      </c>
+      <c r="M250" t="s">
+        <v>62</v>
+      </c>
+      <c r="N250" t="s">
+        <v>2328</v>
+      </c>
+      <c r="O250" t="s">
+        <v>2329</v>
+      </c>
+      <c r="P250" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>66</v>
+      </c>
+      <c r="R250" t="s"/>
+      <c r="S250" t="s">
+        <v>67</v>
+      </c>
+      <c r="T250" t="s">
+        <v>2330</v>
+      </c>
+      <c r="U250" t="s"/>
+      <c r="V250" t="s">
+        <v>2331</v>
+      </c>
+      <c r="W250" t="s"/>
+      <c r="X250" t="s"/>
+      <c r="Y250" t="s"/>
+      <c r="Z250" t="s"/>
+      <c r="AA250" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="251" spans="1:27">
+      <c r="A251" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B251" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C251" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D251" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E251" t="s"/>
+      <c r="F251" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G251" t="s">
+        <v>2336</v>
+      </c>
+      <c r="H251" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I251" t="s">
+        <v>2338</v>
+      </c>
+      <c r="J251" t="s">
+        <v>2339</v>
+      </c>
+      <c r="K251" t="s">
+        <v>60</v>
+      </c>
+      <c r="L251" t="s">
+        <v>2340</v>
+      </c>
+      <c r="M251" t="s">
+        <v>62</v>
+      </c>
+      <c r="N251" t="s">
+        <v>2341</v>
+      </c>
+      <c r="O251" t="s">
+        <v>2342</v>
+      </c>
+      <c r="P251" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q251" t="s"/>
+      <c r="R251" t="s"/>
+      <c r="S251" t="s">
+        <v>67</v>
+      </c>
+      <c r="T251" t="s">
+        <v>2343</v>
+      </c>
+      <c r="U251" t="s"/>
+      <c r="V251" t="s">
+        <v>2344</v>
+      </c>
+      <c r="W251" t="s"/>
+      <c r="X251" t="s"/>
+      <c r="Y251" t="s"/>
+      <c r="Z251" t="s"/>
+      <c r="AA251" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="252" spans="1:27">
+      <c r="A252" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B252" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C252" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D252" t="s">
+        <v>2347</v>
+      </c>
+      <c r="E252" t="s"/>
+      <c r="F252" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G252" t="s">
+        <v>2336</v>
+      </c>
+      <c r="H252" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I252" t="s">
+        <v>2348</v>
+      </c>
+      <c r="J252" t="s">
+        <v>2349</v>
+      </c>
+      <c r="K252" t="s">
+        <v>60</v>
+      </c>
+      <c r="L252" t="s">
+        <v>2350</v>
+      </c>
+      <c r="M252" t="s">
+        <v>62</v>
+      </c>
+      <c r="N252" t="s">
+        <v>2351</v>
+      </c>
+      <c r="O252" t="s">
+        <v>2352</v>
+      </c>
+      <c r="P252" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q252" t="s"/>
+      <c r="R252" t="s"/>
+      <c r="S252" t="s">
+        <v>67</v>
+      </c>
+      <c r="T252" t="s">
+        <v>2353</v>
+      </c>
+      <c r="U252" t="s"/>
+      <c r="V252" t="s">
+        <v>2354</v>
+      </c>
+      <c r="W252" t="s"/>
+      <c r="X252" t="s"/>
+      <c r="Y252" t="s"/>
+      <c r="Z252" t="s"/>
+      <c r="AA252" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="253" spans="1:27">
+      <c r="A253" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B253" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C253" t="s">
+        <v>2357</v>
+      </c>
+      <c r="D253" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E253" t="s"/>
+      <c r="F253" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G253" t="s">
+        <v>2359</v>
+      </c>
+      <c r="H253" t="s">
+        <v>2360</v>
+      </c>
+      <c r="I253" t="s">
+        <v>2361</v>
+      </c>
+      <c r="J253" t="s">
+        <v>2362</v>
+      </c>
+      <c r="K253" t="s">
+        <v>60</v>
+      </c>
+      <c r="L253" t="s">
+        <v>2363</v>
+      </c>
+      <c r="M253" t="s">
+        <v>62</v>
+      </c>
+      <c r="N253" t="s">
+        <v>2364</v>
+      </c>
+      <c r="O253" t="s">
+        <v>2365</v>
+      </c>
+      <c r="P253" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>66</v>
+      </c>
+      <c r="R253" t="s"/>
+      <c r="S253" t="s">
+        <v>67</v>
+      </c>
+      <c r="T253" t="s">
+        <v>2366</v>
+      </c>
+      <c r="U253" t="s"/>
+      <c r="V253" t="s">
+        <v>2367</v>
+      </c>
+      <c r="W253" t="s"/>
+      <c r="X253" t="s"/>
+      <c r="Y253" t="s"/>
+      <c r="Z253" t="s"/>
+      <c r="AA253" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="254" spans="1:27">
+      <c r="A254" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B254" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C254" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D254" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E254" t="s"/>
+      <c r="F254" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G254" t="s">
+        <v>2372</v>
+      </c>
+      <c r="H254" t="s">
+        <v>2373</v>
+      </c>
+      <c r="I254" t="s">
+        <v>2374</v>
+      </c>
+      <c r="J254" t="s">
+        <v>2375</v>
+      </c>
+      <c r="K254" t="s">
+        <v>60</v>
+      </c>
+      <c r="L254" t="s">
+        <v>2376</v>
+      </c>
+      <c r="M254" t="s">
+        <v>62</v>
+      </c>
+      <c r="N254" t="s">
+        <v>2377</v>
+      </c>
+      <c r="O254" t="s">
+        <v>2378</v>
+      </c>
+      <c r="P254" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>66</v>
+      </c>
+      <c r="R254" t="s"/>
+      <c r="S254" t="s">
+        <v>67</v>
+      </c>
+      <c r="T254" t="s">
+        <v>2379</v>
+      </c>
+      <c r="U254" t="s"/>
+      <c r="V254" t="s">
+        <v>2380</v>
+      </c>
+      <c r="W254" t="s"/>
+      <c r="X254" t="s"/>
+      <c r="Y254" t="s"/>
+      <c r="Z254" t="s"/>
+      <c r="AA254" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="255" spans="1:27">
+      <c r="A255" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B255" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C255" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D255" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E255" t="s"/>
+      <c r="F255" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G255" t="s">
+        <v>2372</v>
+      </c>
+      <c r="H255" t="s">
+        <v>2373</v>
+      </c>
+      <c r="I255" t="s">
+        <v>2384</v>
+      </c>
+      <c r="J255" t="s">
+        <v>2385</v>
+      </c>
+      <c r="K255" t="s">
+        <v>60</v>
+      </c>
+      <c r="L255" t="s">
+        <v>2386</v>
+      </c>
+      <c r="M255" t="s">
+        <v>62</v>
+      </c>
+      <c r="N255" t="s">
+        <v>2387</v>
+      </c>
+      <c r="O255" t="s">
+        <v>2388</v>
+      </c>
+      <c r="P255" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>66</v>
+      </c>
+      <c r="R255" t="s"/>
+      <c r="S255" t="s">
+        <v>67</v>
+      </c>
+      <c r="T255" t="s">
+        <v>2389</v>
+      </c>
+      <c r="U255" t="s"/>
+      <c r="V255" t="s">
+        <v>2390</v>
+      </c>
+      <c r="W255" t="s"/>
+      <c r="X255" t="s"/>
+      <c r="Y255" t="s"/>
+      <c r="Z255" t="s"/>
+      <c r="AA255" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="256" spans="1:27">
+      <c r="A256" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B256" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C256" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D256" t="s">
+        <v>2394</v>
+      </c>
+      <c r="E256" t="s"/>
+      <c r="F256" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G256" t="s">
+        <v>2395</v>
+      </c>
+      <c r="H256" t="s">
+        <v>2396</v>
+      </c>
+      <c r="I256" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J256" t="s">
+        <v>2398</v>
+      </c>
+      <c r="K256" t="s">
+        <v>60</v>
+      </c>
+      <c r="L256" t="s">
+        <v>2399</v>
+      </c>
+      <c r="M256" t="s">
+        <v>62</v>
+      </c>
+      <c r="N256" t="s">
+        <v>2400</v>
+      </c>
+      <c r="O256" t="s">
+        <v>2401</v>
+      </c>
+      <c r="P256" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>66</v>
+      </c>
+      <c r="R256" t="s"/>
+      <c r="S256" t="s">
+        <v>67</v>
+      </c>
+      <c r="T256" t="s">
+        <v>2402</v>
+      </c>
+      <c r="U256" t="s"/>
+      <c r="V256" t="s">
+        <v>2403</v>
+      </c>
+      <c r="W256" t="s"/>
+      <c r="X256" t="s"/>
+      <c r="Y256" t="s"/>
+      <c r="Z256" t="s"/>
+      <c r="AA256" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="257" spans="1:27">
+      <c r="A257" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B257" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C257" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D257" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E257" t="s"/>
+      <c r="F257" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G257" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H257" t="s">
+        <v>2408</v>
+      </c>
+      <c r="I257" t="s">
+        <v>2409</v>
+      </c>
+      <c r="J257" t="s">
+        <v>2410</v>
+      </c>
+      <c r="K257" t="s">
+        <v>60</v>
+      </c>
+      <c r="L257" t="s">
+        <v>2411</v>
+      </c>
+      <c r="M257" t="s">
+        <v>62</v>
+      </c>
+      <c r="N257" t="s">
+        <v>2412</v>
+      </c>
+      <c r="O257" t="s">
+        <v>2413</v>
+      </c>
+      <c r="P257" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>66</v>
+      </c>
+      <c r="R257" t="s"/>
+      <c r="S257" t="s">
+        <v>67</v>
+      </c>
+      <c r="T257" t="s">
+        <v>2414</v>
+      </c>
+      <c r="U257" t="s"/>
+      <c r="V257" t="s">
+        <v>2415</v>
+      </c>
+      <c r="W257" t="s"/>
+      <c r="X257" t="s"/>
+      <c r="Y257" t="s"/>
+      <c r="Z257" t="s"/>
+      <c r="AA257" t="n">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/docs/collections/kanok/metadata/data.xlsx
+++ b/docs/collections/kanok/metadata/data.xlsx
@@ -6929,7 +6929,7 @@
     <t>cc96c19e-326e-2e07-5dc6-11820a81a420</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/cc96c19e-326e-2e07-5dc6-11820a81a420</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/cc96c19e-326e-2e07-5dc6-11820a81a420</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4cae4fd2e547b546758d82add1808e28af660576.jpg</t>
@@ -6959,7 +6959,7 @@
     <t>4fb84f65-6f64-3852-2fca-520b41d96f28</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/4fb84f65-6f64-3852-2fca-520b41d96f28</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/4fb84f65-6f64-3852-2fca-520b41d96f28</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4e51d6bb457204b16c45204fc66981f72bcf2b08.jpg</t>
@@ -6998,7 +6998,7 @@
     <t>284d2c19-08d7-a647-051f-a3a0a57f09df</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/284d2c19-08d7-a647-051f-a3a0a57f09df</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/284d2c19-08d7-a647-051f-a3a0a57f09df</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1889baab0424980dfd43217732aa9751ae903b21.jpg</t>
@@ -7037,7 +7037,7 @@
     <t>ee3c9a98-a341-1266-30ee-26484bca854f</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/ee3c9a98-a341-1266-30ee-26484bca854f</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/ee3c9a98-a341-1266-30ee-26484bca854f</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2fc313f10b21aa8a9433994d42cd757205fcc1cc.jpg</t>
@@ -7067,7 +7067,7 @@
     <t>1d431059-3cef-9e24-17e6-eefa2c7fa05b</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/1d431059-3cef-9e24-17e6-eefa2c7fa05b</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/1d431059-3cef-9e24-17e6-eefa2c7fa05b</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1341a7ad2f79d295dc8ee1ac6429e78e44fa7701.jpg</t>
@@ -7106,7 +7106,7 @@
     <t>9417646e-362c-1884-3218-632bb8043503</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9417646e-362c-1884-3218-632bb8043503</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/9417646e-362c-1884-3218-632bb8043503</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/60a35d791c5dc941a572d73effb349a354289c88.jpg</t>
@@ -7145,7 +7145,7 @@
     <t>5e77116c-4884-5ba2-511e-e7fa04cb8cc0</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/5e77116c-4884-5ba2-511e-e7fa04cb8cc0</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/5e77116c-4884-5ba2-511e-e7fa04cb8cc0</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1b6dbaa847b81cf96010dddb778dbe307bb523cb.jpg</t>
@@ -7175,7 +7175,7 @@
     <t>13544e9d-2555-1fbc-2f13-b4a115ca1001</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/13544e9d-2555-1fbc-2f13-b4a115ca1001</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/13544e9d-2555-1fbc-2f13-b4a115ca1001</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3902e809f3629c483dd2141e849ec262f2238dc8.jpg</t>
@@ -7214,7 +7214,7 @@
     <t>60ddc98c-1470-5bb9-0e3c-986694f15d05</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/60ddc98c-1470-5bb9-0e3c-986694f15d05</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/60ddc98c-1470-5bb9-0e3c-986694f15d05</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/82e64328a1bd322962159c850201f16f2324239c.jpg</t>
@@ -7250,7 +7250,7 @@
     <t>c8447634-111b-8162-4c41-bf09167915d2</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/c8447634-111b-8162-4c41-bf09167915d2</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/c8447634-111b-8162-4c41-bf09167915d2</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dd01977d2db3bfd673afb75ec7b7901f19e9ece9.jpg</t>

--- a/docs/collections/kanok/metadata/data.xlsx
+++ b/docs/collections/kanok/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2920">
   <si>
     <t>資料名</t>
   </si>
@@ -7263,6 +7263,1518 @@
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c8447634-111b-8162-4c41-bf09167915d2/manifest</t>
+  </si>
+  <si>
+    <t>帝国大学図書館特許閲覧票</t>
+  </si>
+  <si>
+    <t>1888.09.12</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>博士文書(二)</t>
+  </si>
+  <si>
+    <t>個人関係文書</t>
+  </si>
+  <si>
+    <t>学・東大4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a4924a2c-9b8a-3ace-0752-c67dec9a2101.json</t>
+  </si>
+  <si>
+    <t>a4924a2c-9b8a-3ace-0752-c67dec9a2101</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/a4924a2c-9b8a-3ace-0752-c67dec9a2101</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d9b2a1577ecde69761aa5faf3f2be36b04143a96.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167349</t>
+  </si>
+  <si>
+    <t>0256</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a4924a2c-9b8a-3ace-0752-c67dec9a2101/manifest</t>
+  </si>
+  <si>
+    <t>東京大学図書館規則</t>
+  </si>
+  <si>
+    <t>トウキョウダイガク</t>
+  </si>
+  <si>
+    <t>1884.03</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>学・東大6</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/30a8181e-1fa2-56a8-01ff-5558512a61c0.json</t>
+  </si>
+  <si>
+    <t>30a8181e-1fa2-56a8-01ff-5558512a61c0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/30a8181e-1fa2-56a8-01ff-5558512a61c0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9c347e2c743d6067837b8169a8cbdb3fbb03d65d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167350</t>
+  </si>
+  <si>
+    <t>0257</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/30a8181e-1fa2-56a8-01ff-5558512a61c0/manifest</t>
+  </si>
+  <si>
+    <t>帝国大学図書館閲覧票</t>
+  </si>
+  <si>
+    <t>1891.09</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>学・大学院3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f154418-3672-512a-46df-e221afff759b.json</t>
+  </si>
+  <si>
+    <t>9f154418-3672-512a-46df-e221afff759b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/9f154418-3672-512a-46df-e221afff759b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/03d3f14b0cabdd96eda09ce1e1e504708c9f42b5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167351</t>
+  </si>
+  <si>
+    <t>0258</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f154418-3672-512a-46df-e221afff759b/manifest</t>
+  </si>
+  <si>
+    <t>第一高等学校長就任要請に対しての書翰</t>
+  </si>
+  <si>
+    <t>ダイイチ</t>
+  </si>
+  <si>
+    <t>[1898]</t>
+  </si>
+  <si>
+    <t>封9_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/90b12fe6-9f2d-6deb-4395-dd8c381e8d4c.json</t>
+  </si>
+  <si>
+    <t>90b12fe6-9f2d-6deb-4395-dd8c381e8d4c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/90b12fe6-9f2d-6deb-4395-dd8c381e8d4c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9a39982d5b07882d71feef39f080c6877d9cfff7.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167352</t>
+  </si>
+  <si>
+    <t>0259</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/90b12fe6-9f2d-6deb-4395-dd8c381e8d4c/manifest</t>
+  </si>
+  <si>
+    <t>一高チフス事件に関する書翰</t>
+  </si>
+  <si>
+    <t>イチコウ</t>
+  </si>
+  <si>
+    <t>[1904.03.04]</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>封9_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/186f660c-38cd-4aa1-31f8-288b1d6d1a80.json</t>
+  </si>
+  <si>
+    <t>186f660c-38cd-4aa1-31f8-288b1d6d1a80</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/186f660c-38cd-4aa1-31f8-288b1d6d1a80</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/05801d0cc8c5351a2dc27b214fac259bce655c91.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167353</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/186f660c-38cd-4aa1-31f8-288b1d6d1a80/manifest</t>
+  </si>
+  <si>
+    <t>蔵書目録 仁</t>
+  </si>
+  <si>
+    <t>ゾウショモクロク</t>
+  </si>
+  <si>
+    <t>1894.05.31, 1895.02.15補</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>博士文書(五)</t>
+  </si>
+  <si>
+    <t>書籍鑑定関係文書(五)</t>
+  </si>
+  <si>
+    <t>鑑定(一)2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29edb031-63d8-144a-7d6e-11157d356fc1.json</t>
+  </si>
+  <si>
+    <t>29edb031-63d8-144a-7d6e-11157d356fc1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/29edb031-63d8-144a-7d6e-11157d356fc1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e0e222b1c9246c0be4fca2d581f88382c16ed0ca.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167354</t>
+  </si>
+  <si>
+    <t>0261</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29edb031-63d8-144a-7d6e-11157d356fc1/manifest</t>
+  </si>
+  <si>
+    <t>蔵書目録 義</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>鑑定(一)3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7893e1f2-27d1-3d79-3cdf-c9bc1580a15b.json</t>
+  </si>
+  <si>
+    <t>7893e1f2-27d1-3d79-3cdf-c9bc1580a15b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/7893e1f2-27d1-3d79-3cdf-c9bc1580a15b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fac904f6ae3d20f423f7aba0f42a47284d398270.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167355</t>
+  </si>
+  <si>
+    <t>0262</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7893e1f2-27d1-3d79-3cdf-c9bc1580a15b/manifest</t>
+  </si>
+  <si>
+    <t>蔵書目録 禮</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>鑑定(一)4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c97d255c-713a-87e4-8943-18247bf953da.json</t>
+  </si>
+  <si>
+    <t>c97d255c-713a-87e4-8943-18247bf953da</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/c97d255c-713a-87e4-8943-18247bf953da</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6dc6c871623e669d14343e95c0ed983751c7cfff.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167356</t>
+  </si>
+  <si>
+    <t>0263</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c97d255c-713a-87e4-8943-18247bf953da/manifest</t>
+  </si>
+  <si>
+    <t>蔵書目録 智</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>鑑定(一)5</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/24031b54-2283-1f9e-566a-e7063a325e49.json</t>
+  </si>
+  <si>
+    <t>24031b54-2283-1f9e-566a-e7063a325e49</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/24031b54-2283-1f9e-566a-e7063a325e49</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/01b9c5fbcf79dc79c85d2782d3f6c765d52a71a5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167357</t>
+  </si>
+  <si>
+    <t>0264</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/24031b54-2283-1f9e-566a-e7063a325e49/manifest</t>
+  </si>
+  <si>
+    <t>蔵書目録 信</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>鑑定(一)6</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eef2ff60-6135-74d1-5fd9-c4a68673699e.json</t>
+  </si>
+  <si>
+    <t>eef2ff60-6135-74d1-5fd9-c4a68673699e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/eef2ff60-6135-74d1-5fd9-c4a68673699e</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/96636f648a911302692b1edb5af9c33bccee4af5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167358</t>
+  </si>
+  <si>
+    <t>0265</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eef2ff60-6135-74d1-5fd9-c4a68673699e/manifest</t>
+  </si>
+  <si>
+    <t>書籍目録 明治31年以降追加の部</t>
+  </si>
+  <si>
+    <t>ショセキモクロク</t>
+  </si>
+  <si>
+    <t>1898〜</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>鑑定(一)7</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e83ee199-2de9-71c0-487e-c50fda169eb1.json</t>
+  </si>
+  <si>
+    <t>e83ee199-2de9-71c0-487e-c50fda169eb1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/e83ee199-2de9-71c0-487e-c50fda169eb1</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/90a15742aa14e5fc264ad1bba505f537c2615294.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167359</t>
+  </si>
+  <si>
+    <t>0266</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e83ee199-2de9-71c0-487e-c50fda169eb1/manifest</t>
+  </si>
+  <si>
+    <t>蔵書記之附 暦算書目</t>
+  </si>
+  <si>
+    <t>ゾウショキノフ</t>
+  </si>
+  <si>
+    <t>1885.07〜1886.07</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>鑑定(一)8-1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/98652958-8741-96d7-2f64-4d8c01e21b12.json</t>
+  </si>
+  <si>
+    <t>98652958-8741-96d7-2f64-4d8c01e21b12</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/98652958-8741-96d7-2f64-4d8c01e21b12</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b5dcd691dc4eec8d9aad0808749feef48473e182.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167360</t>
+  </si>
+  <si>
+    <t>0267</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/98652958-8741-96d7-2f64-4d8c01e21b12/manifest</t>
+  </si>
+  <si>
+    <t>暦算推歩書目</t>
+  </si>
+  <si>
+    <t>レキサンスイホ</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>鑑定(一)8-2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a52e5fc9-0586-84f6-2103-b18490559e14.json</t>
+  </si>
+  <si>
+    <t>a52e5fc9-0586-84f6-2103-b18490559e14</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/a52e5fc9-0586-84f6-2103-b18490559e14</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/47964f030edb9f23a8ac296c9199026406ad307b.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167361</t>
+  </si>
+  <si>
+    <t>0268</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a52e5fc9-0586-84f6-2103-b18490559e14/manifest</t>
+  </si>
+  <si>
+    <t>古暦目録</t>
+  </si>
+  <si>
+    <t>コレキモクロク</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>鑑定(一)8-3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/07e9db7a-60ab-4b7e-339e-6997b4b877bc.json</t>
+  </si>
+  <si>
+    <t>07e9db7a-60ab-4b7e-339e-6997b4b877bc</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/07e9db7a-60ab-4b7e-339e-6997b4b877bc</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/063d10b3f2570707a48269913da52bfdeff5f37d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167362</t>
+  </si>
+  <si>
+    <t>0269</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/07e9db7a-60ab-4b7e-339e-6997b4b877bc/manifest</t>
+  </si>
+  <si>
+    <t>蔵書律暦別志</t>
+  </si>
+  <si>
+    <t>ゾウショリツレキ</t>
+  </si>
+  <si>
+    <t>1885.09.13〜1893</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>鑑定(一)8-4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/28f436f6-9943-9d03-1b70-0490198a3097.json</t>
+  </si>
+  <si>
+    <t>28f436f6-9943-9d03-1b70-0490198a3097</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/28f436f6-9943-9d03-1b70-0490198a3097</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f2b0b0de04d87a144fca05fb451cd3cf084f50a3.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167363</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/28f436f6-9943-9d03-1b70-0490198a3097/manifest</t>
+  </si>
+  <si>
+    <t>医書目録</t>
+  </si>
+  <si>
+    <t>イショモクロク</t>
+  </si>
+  <si>
+    <t>鑑定(一)9</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d0f91c99-a280-4bf3-95c9-2def594d42c5.json</t>
+  </si>
+  <si>
+    <t>d0f91c99-a280-4bf3-95c9-2def594d42c5</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/d0f91c99-a280-4bf3-95c9-2def594d42c5</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b88b5e33999b6d344bd1a36175eb847bc50b5dd6.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167364</t>
+  </si>
+  <si>
+    <t>0271</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d0f91c99-a280-4bf3-95c9-2def594d42c5/manifest</t>
+  </si>
+  <si>
+    <t>洋書目録</t>
+  </si>
+  <si>
+    <t>ヨウショモクロク</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>鑑定(一)10-1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/91fec309-1b99-13ec-8e2f-bb1d81e82c92.json</t>
+  </si>
+  <si>
+    <t>91fec309-1b99-13ec-8e2f-bb1d81e82c92</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/91fec309-1b99-13ec-8e2f-bb1d81e82c92</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/006d7c11bdbf005fc753954d87c89f924cfefac9.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167365</t>
+  </si>
+  <si>
+    <t>0272</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/91fec309-1b99-13ec-8e2f-bb1d81e82c92/manifest</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>鑑定(一)10-2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bb1edae-21fe-37e8-50cc-d2664ce857ad.json</t>
+  </si>
+  <si>
+    <t>5bb1edae-21fe-37e8-50cc-d2664ce857ad</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/5bb1edae-21fe-37e8-50cc-d2664ce857ad</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c5604a1c804368c5261acd12e9ad1ee52abda62a.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167366</t>
+  </si>
+  <si>
+    <t>0273</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bb1edae-21fe-37e8-50cc-d2664ce857ad/manifest</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>鑑定(一)10-3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/663aaeca-6454-2df0-93ed-cc91f24796a9.json</t>
+  </si>
+  <si>
+    <t>663aaeca-6454-2df0-93ed-cc91f24796a9</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/663aaeca-6454-2df0-93ed-cc91f24796a9</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9e9b357fd7ac507a48d2775d0551917c596d5508.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167367</t>
+  </si>
+  <si>
+    <t>0274</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/663aaeca-6454-2df0-93ed-cc91f24796a9/manifest</t>
+  </si>
+  <si>
+    <t>図書貸出簿</t>
+  </si>
+  <si>
+    <t>トショカシダシボ</t>
+  </si>
+  <si>
+    <t>[1883].10〜1886.01</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/37620c1d-59bb-506e-a224-09c072b16e53.json</t>
+  </si>
+  <si>
+    <t>37620c1d-59bb-506e-a224-09c072b16e53</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/37620c1d-59bb-506e-a224-09c072b16e53</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/16ec7a80fc289c44dcd91b962d4ef731914405ad.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167368</t>
+  </si>
+  <si>
+    <t>0275</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/37620c1d-59bb-506e-a224-09c072b16e53/manifest</t>
+  </si>
+  <si>
+    <t>書籍借出氏名録</t>
+  </si>
+  <si>
+    <t>ショセキカリダシ</t>
+  </si>
+  <si>
+    <t>1894.05〜</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/68ecc5d4-7641-a011-0a63-3c75bd87a3da.json</t>
+  </si>
+  <si>
+    <t>68ecc5d4-7641-a011-0a63-3c75bd87a3da</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/68ecc5d4-7641-a011-0a63-3c75bd87a3da</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ffee92d9972b2428730d024cdcd947e66444a641.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167369</t>
+  </si>
+  <si>
+    <t>0276</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/68ecc5d4-7641-a011-0a63-3c75bd87a3da/manifest</t>
+  </si>
+  <si>
+    <t>書籍貸出扣簿</t>
+  </si>
+  <si>
+    <t>ショセキカシダシ</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cbdd5a02-1909-46c0-0560-3f249f083997.json</t>
+  </si>
+  <si>
+    <t>cbdd5a02-1909-46c0-0560-3f249f083997</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/cbdd5a02-1909-46c0-0560-3f249f083997</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f3a5f1f3b015206924514f20522f8aa2ebda09b1.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167370</t>
+  </si>
+  <si>
+    <t>0277</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cbdd5a02-1909-46c0-0560-3f249f083997/manifest</t>
+  </si>
+  <si>
+    <t>狩野家図書貸出簿</t>
+  </si>
+  <si>
+    <t>カノウケトショ</t>
+  </si>
+  <si>
+    <t>1907.05〜1919.01.10</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f9f666c-49a4-54d2-1b40-646e6d7297a0.json</t>
+  </si>
+  <si>
+    <t>9f9f666c-49a4-54d2-1b40-646e6d7297a0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/9f9f666c-49a4-54d2-1b40-646e6d7297a0</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aa92a0bb36c4f642de9ec09c1c292d86ad72841d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167371</t>
+  </si>
+  <si>
+    <t>0278</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f9f666c-49a4-54d2-1b40-646e6d7297a0/manifest</t>
+  </si>
+  <si>
+    <t>京都ヘ携フ書類目録</t>
+  </si>
+  <si>
+    <t>キョウトヘタズサウ</t>
+  </si>
+  <si>
+    <t>1907.09</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-5</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/24bb7486-436c-a1bc-6a01-d1076e60716a.json</t>
+  </si>
+  <si>
+    <t>24bb7486-436c-a1bc-6a01-d1076e60716a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/24bb7486-436c-a1bc-6a01-d1076e60716a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b7990149d1ab46635eb9f311ceee2bdb5f629bb2.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167372</t>
+  </si>
+  <si>
+    <t>0279</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/24bb7486-436c-a1bc-6a01-d1076e60716a/manifest</t>
+  </si>
+  <si>
+    <t>書籍貸出控</t>
+  </si>
+  <si>
+    <t>1936.06.01〜1942.11.18</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-6</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4d20f7ff-5e8e-4b10-1358-e7f0ca38237a.json</t>
+  </si>
+  <si>
+    <t>4d20f7ff-5e8e-4b10-1358-e7f0ca38237a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/4d20f7ff-5e8e-4b10-1358-e7f0ca38237a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8e4cb446927b430215cfff89a101cb88eb78e068.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167373</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4d20f7ff-5e8e-4b10-1358-e7f0ca38237a/manifest</t>
+  </si>
+  <si>
+    <t>1907.09.01, 1920.05.04, ????.06.19</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-7_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/89946319-21da-5307-6d56-251f3c56037a.json</t>
+  </si>
+  <si>
+    <t>89946319-21da-5307-6d56-251f3c56037a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/89946319-21da-5307-6d56-251f3c56037a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/836f8cd6ab038778f91a80e1ca4fd307d20d8e0b.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167374</t>
+  </si>
+  <si>
+    <t>0281</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/89946319-21da-5307-6d56-251f3c56037a/manifest</t>
+  </si>
+  <si>
+    <t>1920.02.17, ????.04.05, ????.09.11</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-7_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1ebb02ce-9887-0509-7fb4-acb814fc59bf.json</t>
+  </si>
+  <si>
+    <t>1ebb02ce-9887-0509-7fb4-acb814fc59bf</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/1ebb02ce-9887-0509-7fb4-acb814fc59bf</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f6e7daef4886cb69248f7c76ca6cc998d2c9a9bc.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167375</t>
+  </si>
+  <si>
+    <t>0282</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1ebb02ce-9887-0509-7fb4-acb814fc59bf/manifest</t>
+  </si>
+  <si>
+    <t>1908.10.15, 1909.02.18</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-7_3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e080a4fb-2e48-5fca-5e32-c1e2a8364963.json</t>
+  </si>
+  <si>
+    <t>e080a4fb-2e48-5fca-5e32-c1e2a8364963</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/e080a4fb-2e48-5fca-5e32-c1e2a8364963</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2864541934fbe31b70ace11de27b7d3307b425a2.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167376</t>
+  </si>
+  <si>
+    <t>0283</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e080a4fb-2e48-5fca-5e32-c1e2a8364963/manifest</t>
+  </si>
+  <si>
+    <t>1912, 1907.07.23, ????.9.11〜24</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-7_4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/de43e6b1-3a60-0b91-a1a7-7bcba1d53f6b.json</t>
+  </si>
+  <si>
+    <t>de43e6b1-3a60-0b91-a1a7-7bcba1d53f6b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/de43e6b1-3a60-0b91-a1a7-7bcba1d53f6b</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b5e1bf89b7cdcb77200b822daae90c5bf2a7f9c3.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167377</t>
+  </si>
+  <si>
+    <t>0284</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/de43e6b1-3a60-0b91-a1a7-7bcba1d53f6b/manifest</t>
+  </si>
+  <si>
+    <t>名刺(書籍貸借についてのメモ)</t>
+  </si>
+  <si>
+    <t>メイシ</t>
+  </si>
+  <si>
+    <t>????.11.17, 1912.10.25</t>
+  </si>
+  <si>
+    <t>鑑定(一)11-7_5</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4eb84a91-960b-8db1-7ca5-caa63c8a92b4.json</t>
+  </si>
+  <si>
+    <t>4eb84a91-960b-8db1-7ca5-caa63c8a92b4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/4eb84a91-960b-8db1-7ca5-caa63c8a92b4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9ab3bee9171775b2ca4f11731096145d43cb204e.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167378</t>
+  </si>
+  <si>
+    <t>0285</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4eb84a91-960b-8db1-7ca5-caa63c8a92b4/manifest</t>
+  </si>
+  <si>
+    <t>送本扣</t>
+  </si>
+  <si>
+    <t>ソウホンヒカエ</t>
+  </si>
+  <si>
+    <t>1912.10.02〜1917.04.09</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>鑑定(五)1_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/80060d38-73de-1be3-41de-9b0aacab7f77.json</t>
+  </si>
+  <si>
+    <t>80060d38-73de-1be3-41de-9b0aacab7f77</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/80060d38-73de-1be3-41de-9b0aacab7f77</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3048130ba0f76b8083c4a8dff9d2d94a842f36b2.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167379</t>
+  </si>
+  <si>
+    <t>0286</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/80060d38-73de-1be3-41de-9b0aacab7f77/manifest</t>
+  </si>
+  <si>
+    <t>東北帝国大学図書館への寄贈目録</t>
+  </si>
+  <si>
+    <t>トウホクテイコク</t>
+  </si>
+  <si>
+    <t>1912.01.05, 1916.02.07, 1916.05.23, 1917.06</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>鑑定(五)1_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5ee4035e-6417-1b81-5b19-1a3b63e88b4f.json</t>
+  </si>
+  <si>
+    <t>5ee4035e-6417-1b81-5b19-1a3b63e88b4f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/5ee4035e-6417-1b81-5b19-1a3b63e88b4f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4bbc8ee2909672501337841e2b88c19e16a03fb8.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167380</t>
+  </si>
+  <si>
+    <t>0287</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5ee4035e-6417-1b81-5b19-1a3b63e88b4f/manifest</t>
+  </si>
+  <si>
+    <t>東北帝国大学図書館宛電報草稿</t>
+  </si>
+  <si>
+    <t>[1923.06.18]</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>鑑定(五)1_3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/24734f3c-9400-2ef1-9f1e-9bf288960b2f.json</t>
+  </si>
+  <si>
+    <t>24734f3c-9400-2ef1-9f1e-9bf288960b2f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/24734f3c-9400-2ef1-9f1e-9bf288960b2f</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e91decbc238dadc49c256b9d821766d51c5ed3ad.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167381</t>
+  </si>
+  <si>
+    <t>0288</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/24734f3c-9400-2ef1-9f1e-9bf288960b2f/manifest</t>
+  </si>
+  <si>
+    <t>狩野氏寄贈目録(東北帝国大学作成)</t>
+  </si>
+  <si>
+    <t>カノウシキゾウ</t>
+  </si>
+  <si>
+    <t>1924.06.21</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>鑑定(五)2_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c458ddc0-8a0c-a02c-4687-1b78fb5d00e4.json</t>
+  </si>
+  <si>
+    <t>c458ddc0-8a0c-a02c-4687-1b78fb5d00e4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/c458ddc0-8a0c-a02c-4687-1b78fb5d00e4</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d83313dbb99e06efc5a0a7228afc07b590cd1bc5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167382</t>
+  </si>
+  <si>
+    <t>0289</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c458ddc0-8a0c-a02c-4687-1b78fb5d00e4/manifest</t>
+  </si>
+  <si>
+    <t>東北大学ヘ寄贈ノ書目録(狩野亨吉作成)</t>
+  </si>
+  <si>
+    <t>トウホクダイガク</t>
+  </si>
+  <si>
+    <t>鑑定(五)2_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f0db172f-a77e-1bde-2a4f-8eb798e6630c.json</t>
+  </si>
+  <si>
+    <t>f0db172f-a77e-1bde-2a4f-8eb798e6630c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/f0db172f-a77e-1bde-2a4f-8eb798e6630c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0623a929b335fa69b87121df509b7707a93df3a0.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167383</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f0db172f-a77e-1bde-2a4f-8eb798e6630c/manifest</t>
+  </si>
+  <si>
+    <t>九州帝国大学医学部眼科教室納入書目</t>
+  </si>
+  <si>
+    <t>キュウシュウ</t>
+  </si>
+  <si>
+    <t>1921.03〜1925.02</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>鑑定(五)3_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1d628102-8108-772f-62bd-780d7b05003c.json</t>
+  </si>
+  <si>
+    <t>1d628102-8108-772f-62bd-780d7b05003c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/1d628102-8108-772f-62bd-780d7b05003c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/64ded6293d600391d0b480231874ccf28720196a.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167384</t>
+  </si>
+  <si>
+    <t>0291</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1d628102-8108-772f-62bd-780d7b05003c/manifest</t>
+  </si>
+  <si>
+    <t>九州帝国大学医書目録</t>
+  </si>
+  <si>
+    <t>1921.08〜</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>鑑定(五)3_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/44db827e-a4c3-625e-4d65-9578ded48f6a.json</t>
+  </si>
+  <si>
+    <t>44db827e-a4c3-625e-4d65-9578ded48f6a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/44db827e-a4c3-625e-4d65-9578ded48f6a</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f9bad882f3f26065c7f0d72232b9efa5c54c1f34.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167385</t>
+  </si>
+  <si>
+    <t>0292</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/44db827e-a4c3-625e-4d65-9578ded48f6a/manifest</t>
+  </si>
+  <si>
+    <t>九大眼科教室納入図書関係書類 書物一冊付</t>
+  </si>
+  <si>
+    <t>キュウダイ</t>
+  </si>
+  <si>
+    <t>1921.03.13〜1922.11.02</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>鑑定(五)3_3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9271e4f7-53de-58f0-77ae-f34bcba12b0d.json</t>
+  </si>
+  <si>
+    <t>9271e4f7-53de-58f0-77ae-f34bcba12b0d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/9271e4f7-53de-58f0-77ae-f34bcba12b0d</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f843a46a4bd2356fbc94b0bb51c5ff547124ad0f.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167386</t>
+  </si>
+  <si>
+    <t>0293</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9271e4f7-53de-58f0-77ae-f34bcba12b0d/manifest</t>
+  </si>
+  <si>
+    <t>入札図書目録仮原稿(狩野家)</t>
+  </si>
+  <si>
+    <t>ニュウサツ</t>
+  </si>
+  <si>
+    <t>1922.04</t>
+  </si>
+  <si>
+    <t>鑑定(五)4_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/afb8e367-986f-3133-7e04-aff0d1a83859.json</t>
+  </si>
+  <si>
+    <t>afb8e367-986f-3133-7e04-aff0d1a83859</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/afb8e367-986f-3133-7e04-aff0d1a83859</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/172133a343a31e66035d34240743cff7420085f1.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167387</t>
+  </si>
+  <si>
+    <t>0294</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/afb8e367-986f-3133-7e04-aff0d1a83859/manifest</t>
+  </si>
+  <si>
+    <t>狩野亨吉氏蔵書売立展覧目録(下書)</t>
+  </si>
+  <si>
+    <t>カノウコウキチシ</t>
+  </si>
+  <si>
+    <t>[1922]</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>鑑定(五)4_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5ac81bcd-8536-81d5-82c2-e4fe12327e20.json</t>
+  </si>
+  <si>
+    <t>5ac81bcd-8536-81d5-82c2-e4fe12327e20</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/5ac81bcd-8536-81d5-82c2-e4fe12327e20</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7aaaabff9c8e7e58450ea4973f3702ed3deaeb5c.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167388</t>
+  </si>
+  <si>
+    <t>0295</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5ac81bcd-8536-81d5-82c2-e4fe12327e20/manifest</t>
+  </si>
+  <si>
+    <t>狩野亨吉氏蔵書売立展覧目録</t>
+  </si>
+  <si>
+    <t>[1922.4.25]</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>鑑定(五)4_3</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eb29c09f-49b3-24ae-97cc-0e0aaf1a1111.json</t>
+  </si>
+  <si>
+    <t>eb29c09f-49b3-24ae-97cc-0e0aaf1a1111</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/eb29c09f-49b3-24ae-97cc-0e0aaf1a1111</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17911eaee9031b73e3b97368de933796c1047815.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167389</t>
+  </si>
+  <si>
+    <t>0296</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eb29c09f-49b3-24ae-97cc-0e0aaf1a1111/manifest</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>鑑定(五)4_4</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e00775a0-a39e-3c69-8376-2e6a072c37a2.json</t>
+  </si>
+  <si>
+    <t>e00775a0-a39e-3c69-8376-2e6a072c37a2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/e00775a0-a39e-3c69-8376-2e6a072c37a2</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f770f67b81b4a8aa39da3bd5ed8d52545b2b8fd8.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167390</t>
+  </si>
+  <si>
+    <t>0297</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e00775a0-a39e-3c69-8376-2e6a072c37a2/manifest</t>
+  </si>
+  <si>
+    <t>狩野亨吉氏蔵書売立展覧目録(表装付)</t>
+  </si>
+  <si>
+    <t>ゾウショウリタテ</t>
+  </si>
+  <si>
+    <t>1922</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>鑑定(五)4_5</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a3873844-98b6-7b7a-a40b-66b62c1ba643.json</t>
+  </si>
+  <si>
+    <t>a3873844-98b6-7b7a-a40b-66b62c1ba643</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/a3873844-98b6-7b7a-a40b-66b62c1ba643</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5b544d2f3be0950502256b752f16c664b6e169cf.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167391</t>
+  </si>
+  <si>
+    <t>0298</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a3873844-98b6-7b7a-a40b-66b62c1ba643/manifest</t>
+  </si>
+  <si>
+    <t>蔵書売立山帳 第壱号</t>
+  </si>
+  <si>
+    <t>1922.04.26</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>鑑定(五)5_1</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/956323a0-04fd-12a3-8dd5-9715fe774423.json</t>
+  </si>
+  <si>
+    <t>956323a0-04fd-12a3-8dd5-9715fe774423</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/956323a0-04fd-12a3-8dd5-9715fe774423</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7af5e2c0b4817c647af284dbc74b3074ba5fb0ff.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167392</t>
+  </si>
+  <si>
+    <t>0299</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/956323a0-04fd-12a3-8dd5-9715fe774423/manifest</t>
+  </si>
+  <si>
+    <t>蔵書売立山帳 第弐号</t>
+  </si>
+  <si>
+    <t>1922.04.27</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>鑑定(五)5_2</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/75ffbe29-4428-0ea8-1e5a-60b3c2a98704.json</t>
+  </si>
+  <si>
+    <t>75ffbe29-4428-0ea8-1e5a-60b3c2a98704</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/75ffbe29-4428-0ea8-1e5a-60b3c2a98704</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e733ae433b5b535a60b00515fced0c423b8db46.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167393</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/75ffbe29-4428-0ea8-1e5a-60b3c2a98704/manifest</t>
+  </si>
+  <si>
+    <t>日比谷図書館ニ買上錦絵類目録</t>
+  </si>
+  <si>
+    <t>ヒビヤトショカン</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>鑑定(五)6</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/291b3e67-1e76-38c6-65f9-6342c40d705c.json</t>
+  </si>
+  <si>
+    <t>291b3e67-1e76-38c6-65f9-6342c40d705c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/291b3e67-1e76-38c6-65f9-6342c40d705c</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6a298d927cd111bc22301dd149339bd5dd5257e1.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167394</t>
+  </si>
+  <si>
+    <t>0301</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/291b3e67-1e76-38c6-65f9-6342c40d705c/manifest</t>
   </si>
 </sst>
 </file>
@@ -7598,7 +9110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA257"/>
+  <dimension ref="A1:AA303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -7764,7 +9276,7 @@
         <v>51</v>
       </c>
       <c r="AA2" t="n">
-        <v>1687</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -24848,6 +26360,3156 @@
         <v>83</v>
       </c>
     </row>
+    <row r="258" spans="1:27">
+      <c r="A258" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C258" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D258" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E258" t="s"/>
+      <c r="F258" t="s">
+        <v>2419</v>
+      </c>
+      <c r="G258" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H258" t="s">
+        <v>2421</v>
+      </c>
+      <c r="I258" t="s">
+        <v>2422</v>
+      </c>
+      <c r="J258" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K258" t="s">
+        <v>60</v>
+      </c>
+      <c r="L258" t="s">
+        <v>2424</v>
+      </c>
+      <c r="M258" t="s">
+        <v>62</v>
+      </c>
+      <c r="N258" t="s">
+        <v>2425</v>
+      </c>
+      <c r="O258" t="s">
+        <v>2426</v>
+      </c>
+      <c r="P258" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>66</v>
+      </c>
+      <c r="R258" t="s"/>
+      <c r="S258" t="s">
+        <v>67</v>
+      </c>
+      <c r="T258" t="s">
+        <v>2427</v>
+      </c>
+      <c r="U258" t="s"/>
+      <c r="V258" t="s">
+        <v>2428</v>
+      </c>
+      <c r="W258" t="s"/>
+      <c r="X258" t="s"/>
+      <c r="Y258" t="s"/>
+      <c r="Z258" t="s"/>
+      <c r="AA258" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:27">
+      <c r="A259" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B259" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C259" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D259" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E259" t="s"/>
+      <c r="F259" t="s">
+        <v>2419</v>
+      </c>
+      <c r="G259" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H259" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I259" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J259" t="s">
+        <v>2435</v>
+      </c>
+      <c r="K259" t="s">
+        <v>60</v>
+      </c>
+      <c r="L259" t="s">
+        <v>2436</v>
+      </c>
+      <c r="M259" t="s">
+        <v>62</v>
+      </c>
+      <c r="N259" t="s">
+        <v>2437</v>
+      </c>
+      <c r="O259" t="s">
+        <v>2438</v>
+      </c>
+      <c r="P259" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>66</v>
+      </c>
+      <c r="R259" t="s"/>
+      <c r="S259" t="s">
+        <v>67</v>
+      </c>
+      <c r="T259" t="s">
+        <v>2439</v>
+      </c>
+      <c r="U259" t="s"/>
+      <c r="V259" t="s">
+        <v>2440</v>
+      </c>
+      <c r="W259" t="s"/>
+      <c r="X259" t="s"/>
+      <c r="Y259" t="s"/>
+      <c r="Z259" t="s"/>
+      <c r="AA259" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" spans="1:27">
+      <c r="A260" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C260" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D260" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E260" t="s"/>
+      <c r="F260" t="s">
+        <v>2419</v>
+      </c>
+      <c r="G260" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H260" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I260" t="s">
+        <v>2445</v>
+      </c>
+      <c r="J260" t="s">
+        <v>2446</v>
+      </c>
+      <c r="K260" t="s">
+        <v>60</v>
+      </c>
+      <c r="L260" t="s">
+        <v>2447</v>
+      </c>
+      <c r="M260" t="s">
+        <v>62</v>
+      </c>
+      <c r="N260" t="s">
+        <v>2448</v>
+      </c>
+      <c r="O260" t="s">
+        <v>2449</v>
+      </c>
+      <c r="P260" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>66</v>
+      </c>
+      <c r="R260" t="s"/>
+      <c r="S260" t="s">
+        <v>67</v>
+      </c>
+      <c r="T260" t="s">
+        <v>2450</v>
+      </c>
+      <c r="U260" t="s"/>
+      <c r="V260" t="s">
+        <v>2451</v>
+      </c>
+      <c r="W260" t="s"/>
+      <c r="X260" t="s"/>
+      <c r="Y260" t="s"/>
+      <c r="Z260" t="s"/>
+      <c r="AA260" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:27">
+      <c r="A261" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B261" t="s">
+        <v>2453</v>
+      </c>
+      <c r="C261" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D261" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E261" t="s"/>
+      <c r="F261" t="s">
+        <v>2419</v>
+      </c>
+      <c r="G261" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H261" t="s">
+        <v>2455</v>
+      </c>
+      <c r="I261" t="s">
+        <v>2456</v>
+      </c>
+      <c r="J261" t="s">
+        <v>2457</v>
+      </c>
+      <c r="K261" t="s">
+        <v>60</v>
+      </c>
+      <c r="L261" t="s">
+        <v>2458</v>
+      </c>
+      <c r="M261" t="s">
+        <v>62</v>
+      </c>
+      <c r="N261" t="s">
+        <v>2459</v>
+      </c>
+      <c r="O261" t="s">
+        <v>2460</v>
+      </c>
+      <c r="P261" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>66</v>
+      </c>
+      <c r="R261" t="s"/>
+      <c r="S261" t="s">
+        <v>67</v>
+      </c>
+      <c r="T261" t="s">
+        <v>2461</v>
+      </c>
+      <c r="U261" t="s"/>
+      <c r="V261" t="s">
+        <v>2462</v>
+      </c>
+      <c r="W261" t="s"/>
+      <c r="X261" t="s"/>
+      <c r="Y261" t="s"/>
+      <c r="Z261" t="s"/>
+      <c r="AA261" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:27">
+      <c r="A262" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B262" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C262" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D262" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E262" t="s"/>
+      <c r="F262" t="s">
+        <v>2419</v>
+      </c>
+      <c r="G262" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H262" t="s">
+        <v>2467</v>
+      </c>
+      <c r="I262" t="s">
+        <v>2468</v>
+      </c>
+      <c r="J262" t="s">
+        <v>2469</v>
+      </c>
+      <c r="K262" t="s">
+        <v>60</v>
+      </c>
+      <c r="L262" t="s">
+        <v>2470</v>
+      </c>
+      <c r="M262" t="s">
+        <v>62</v>
+      </c>
+      <c r="N262" t="s">
+        <v>2471</v>
+      </c>
+      <c r="O262" t="s">
+        <v>2472</v>
+      </c>
+      <c r="P262" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>66</v>
+      </c>
+      <c r="R262" t="s"/>
+      <c r="S262" t="s">
+        <v>67</v>
+      </c>
+      <c r="T262" t="s">
+        <v>2473</v>
+      </c>
+      <c r="U262" t="s"/>
+      <c r="V262" t="s">
+        <v>2474</v>
+      </c>
+      <c r="W262" t="s"/>
+      <c r="X262" t="s"/>
+      <c r="Y262" t="s"/>
+      <c r="Z262" t="s"/>
+      <c r="AA262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:27">
+      <c r="A263" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B263" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C263" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D263" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E263" t="s"/>
+      <c r="F263" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G263" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H263" t="s">
+        <v>2481</v>
+      </c>
+      <c r="I263" t="s">
+        <v>2482</v>
+      </c>
+      <c r="J263" t="s">
+        <v>2483</v>
+      </c>
+      <c r="K263" t="s">
+        <v>60</v>
+      </c>
+      <c r="L263" t="s">
+        <v>2484</v>
+      </c>
+      <c r="M263" t="s">
+        <v>62</v>
+      </c>
+      <c r="N263" t="s">
+        <v>2485</v>
+      </c>
+      <c r="O263" t="s">
+        <v>2486</v>
+      </c>
+      <c r="P263" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>66</v>
+      </c>
+      <c r="R263" t="s"/>
+      <c r="S263" t="s">
+        <v>67</v>
+      </c>
+      <c r="T263" t="s">
+        <v>2487</v>
+      </c>
+      <c r="U263" t="s"/>
+      <c r="V263" t="s">
+        <v>2488</v>
+      </c>
+      <c r="W263" t="s"/>
+      <c r="X263" t="s"/>
+      <c r="Y263" t="s"/>
+      <c r="Z263" t="s"/>
+      <c r="AA263" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="264" spans="1:27">
+      <c r="A264" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B264" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C264" t="s"/>
+      <c r="D264" t="s">
+        <v>2490</v>
+      </c>
+      <c r="E264" t="s"/>
+      <c r="F264" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G264" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H264" t="s">
+        <v>2491</v>
+      </c>
+      <c r="I264" t="s">
+        <v>2492</v>
+      </c>
+      <c r="J264" t="s">
+        <v>2493</v>
+      </c>
+      <c r="K264" t="s">
+        <v>60</v>
+      </c>
+      <c r="L264" t="s">
+        <v>2494</v>
+      </c>
+      <c r="M264" t="s">
+        <v>62</v>
+      </c>
+      <c r="N264" t="s">
+        <v>2495</v>
+      </c>
+      <c r="O264" t="s">
+        <v>2496</v>
+      </c>
+      <c r="P264" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>66</v>
+      </c>
+      <c r="R264" t="s"/>
+      <c r="S264" t="s">
+        <v>67</v>
+      </c>
+      <c r="T264" t="s">
+        <v>2497</v>
+      </c>
+      <c r="U264" t="s"/>
+      <c r="V264" t="s">
+        <v>2498</v>
+      </c>
+      <c r="W264" t="s"/>
+      <c r="X264" t="s"/>
+      <c r="Y264" t="s"/>
+      <c r="Z264" t="s"/>
+      <c r="AA264" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="265" spans="1:27">
+      <c r="A265" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B265" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C265" t="s"/>
+      <c r="D265" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E265" t="s"/>
+      <c r="F265" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G265" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H265" t="s">
+        <v>2501</v>
+      </c>
+      <c r="I265" t="s">
+        <v>2502</v>
+      </c>
+      <c r="J265" t="s">
+        <v>2503</v>
+      </c>
+      <c r="K265" t="s">
+        <v>60</v>
+      </c>
+      <c r="L265" t="s">
+        <v>2504</v>
+      </c>
+      <c r="M265" t="s">
+        <v>62</v>
+      </c>
+      <c r="N265" t="s">
+        <v>2505</v>
+      </c>
+      <c r="O265" t="s">
+        <v>2506</v>
+      </c>
+      <c r="P265" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>66</v>
+      </c>
+      <c r="R265" t="s"/>
+      <c r="S265" t="s">
+        <v>67</v>
+      </c>
+      <c r="T265" t="s">
+        <v>2507</v>
+      </c>
+      <c r="U265" t="s"/>
+      <c r="V265" t="s">
+        <v>2508</v>
+      </c>
+      <c r="W265" t="s"/>
+      <c r="X265" t="s"/>
+      <c r="Y265" t="s"/>
+      <c r="Z265" t="s"/>
+      <c r="AA265" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="266" spans="1:27">
+      <c r="A266" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B266" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C266" t="s"/>
+      <c r="D266" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E266" t="s"/>
+      <c r="F266" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G266" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H266" t="s">
+        <v>2511</v>
+      </c>
+      <c r="I266" t="s">
+        <v>2512</v>
+      </c>
+      <c r="J266" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K266" t="s">
+        <v>60</v>
+      </c>
+      <c r="L266" t="s">
+        <v>2514</v>
+      </c>
+      <c r="M266" t="s">
+        <v>62</v>
+      </c>
+      <c r="N266" t="s">
+        <v>2515</v>
+      </c>
+      <c r="O266" t="s">
+        <v>2516</v>
+      </c>
+      <c r="P266" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>66</v>
+      </c>
+      <c r="R266" t="s"/>
+      <c r="S266" t="s">
+        <v>67</v>
+      </c>
+      <c r="T266" t="s">
+        <v>2517</v>
+      </c>
+      <c r="U266" t="s"/>
+      <c r="V266" t="s">
+        <v>2518</v>
+      </c>
+      <c r="W266" t="s"/>
+      <c r="X266" t="s"/>
+      <c r="Y266" t="s"/>
+      <c r="Z266" t="s"/>
+      <c r="AA266" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="267" spans="1:27">
+      <c r="A267" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B267" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C267" t="s"/>
+      <c r="D267" t="s">
+        <v>2520</v>
+      </c>
+      <c r="E267" t="s"/>
+      <c r="F267" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G267" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H267" t="s">
+        <v>2521</v>
+      </c>
+      <c r="I267" t="s">
+        <v>2522</v>
+      </c>
+      <c r="J267" t="s">
+        <v>2523</v>
+      </c>
+      <c r="K267" t="s">
+        <v>60</v>
+      </c>
+      <c r="L267" t="s">
+        <v>2524</v>
+      </c>
+      <c r="M267" t="s">
+        <v>62</v>
+      </c>
+      <c r="N267" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O267" t="s">
+        <v>2526</v>
+      </c>
+      <c r="P267" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>66</v>
+      </c>
+      <c r="R267" t="s"/>
+      <c r="S267" t="s">
+        <v>67</v>
+      </c>
+      <c r="T267" t="s">
+        <v>2527</v>
+      </c>
+      <c r="U267" t="s"/>
+      <c r="V267" t="s">
+        <v>2528</v>
+      </c>
+      <c r="W267" t="s"/>
+      <c r="X267" t="s"/>
+      <c r="Y267" t="s"/>
+      <c r="Z267" t="s"/>
+      <c r="AA267" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="268" spans="1:27">
+      <c r="A268" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B268" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C268" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D268" t="s">
+        <v>2532</v>
+      </c>
+      <c r="E268" t="s"/>
+      <c r="F268" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G268" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H268" t="s">
+        <v>2533</v>
+      </c>
+      <c r="I268" t="s">
+        <v>2534</v>
+      </c>
+      <c r="J268" t="s">
+        <v>2535</v>
+      </c>
+      <c r="K268" t="s">
+        <v>60</v>
+      </c>
+      <c r="L268" t="s">
+        <v>2536</v>
+      </c>
+      <c r="M268" t="s">
+        <v>62</v>
+      </c>
+      <c r="N268" t="s">
+        <v>2537</v>
+      </c>
+      <c r="O268" t="s">
+        <v>2538</v>
+      </c>
+      <c r="P268" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>66</v>
+      </c>
+      <c r="R268" t="s"/>
+      <c r="S268" t="s">
+        <v>67</v>
+      </c>
+      <c r="T268" t="s">
+        <v>2539</v>
+      </c>
+      <c r="U268" t="s"/>
+      <c r="V268" t="s">
+        <v>2540</v>
+      </c>
+      <c r="W268" t="s"/>
+      <c r="X268" t="s"/>
+      <c r="Y268" t="s"/>
+      <c r="Z268" t="s"/>
+      <c r="AA268" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="269" spans="1:27">
+      <c r="A269" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B269" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C269" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D269" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E269" t="s"/>
+      <c r="F269" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G269" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H269" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I269" t="s">
+        <v>2546</v>
+      </c>
+      <c r="J269" t="s">
+        <v>2547</v>
+      </c>
+      <c r="K269" t="s">
+        <v>60</v>
+      </c>
+      <c r="L269" t="s">
+        <v>2548</v>
+      </c>
+      <c r="M269" t="s">
+        <v>62</v>
+      </c>
+      <c r="N269" t="s">
+        <v>2549</v>
+      </c>
+      <c r="O269" t="s">
+        <v>2550</v>
+      </c>
+      <c r="P269" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>66</v>
+      </c>
+      <c r="R269" t="s"/>
+      <c r="S269" t="s">
+        <v>67</v>
+      </c>
+      <c r="T269" t="s">
+        <v>2551</v>
+      </c>
+      <c r="U269" t="s"/>
+      <c r="V269" t="s">
+        <v>2552</v>
+      </c>
+      <c r="W269" t="s"/>
+      <c r="X269" t="s"/>
+      <c r="Y269" t="s"/>
+      <c r="Z269" t="s"/>
+      <c r="AA269" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:27">
+      <c r="A270" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B270" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C270" t="s"/>
+      <c r="D270" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E270" t="s"/>
+      <c r="F270" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G270" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H270" t="s">
+        <v>2556</v>
+      </c>
+      <c r="I270" t="s">
+        <v>2557</v>
+      </c>
+      <c r="J270" t="s">
+        <v>2558</v>
+      </c>
+      <c r="K270" t="s">
+        <v>60</v>
+      </c>
+      <c r="L270" t="s">
+        <v>2559</v>
+      </c>
+      <c r="M270" t="s">
+        <v>62</v>
+      </c>
+      <c r="N270" t="s">
+        <v>2560</v>
+      </c>
+      <c r="O270" t="s">
+        <v>2561</v>
+      </c>
+      <c r="P270" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>66</v>
+      </c>
+      <c r="R270" t="s"/>
+      <c r="S270" t="s">
+        <v>67</v>
+      </c>
+      <c r="T270" t="s">
+        <v>2562</v>
+      </c>
+      <c r="U270" t="s"/>
+      <c r="V270" t="s">
+        <v>2563</v>
+      </c>
+      <c r="W270" t="s"/>
+      <c r="X270" t="s"/>
+      <c r="Y270" t="s"/>
+      <c r="Z270" t="s"/>
+      <c r="AA270" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:27">
+      <c r="A271" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B271" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C271" t="s"/>
+      <c r="D271" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E271" t="s"/>
+      <c r="F271" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G271" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H271" t="s">
+        <v>2567</v>
+      </c>
+      <c r="I271" t="s">
+        <v>2568</v>
+      </c>
+      <c r="J271" t="s">
+        <v>2569</v>
+      </c>
+      <c r="K271" t="s">
+        <v>60</v>
+      </c>
+      <c r="L271" t="s">
+        <v>2570</v>
+      </c>
+      <c r="M271" t="s">
+        <v>62</v>
+      </c>
+      <c r="N271" t="s">
+        <v>2571</v>
+      </c>
+      <c r="O271" t="s">
+        <v>2572</v>
+      </c>
+      <c r="P271" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>66</v>
+      </c>
+      <c r="R271" t="s"/>
+      <c r="S271" t="s">
+        <v>67</v>
+      </c>
+      <c r="T271" t="s">
+        <v>2573</v>
+      </c>
+      <c r="U271" t="s"/>
+      <c r="V271" t="s">
+        <v>2574</v>
+      </c>
+      <c r="W271" t="s"/>
+      <c r="X271" t="s"/>
+      <c r="Y271" t="s"/>
+      <c r="Z271" t="s"/>
+      <c r="AA271" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:27">
+      <c r="A272" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B272" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C272" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D272" t="s">
+        <v>2578</v>
+      </c>
+      <c r="E272" t="s"/>
+      <c r="F272" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G272" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H272" t="s">
+        <v>2579</v>
+      </c>
+      <c r="I272" t="s">
+        <v>2580</v>
+      </c>
+      <c r="J272" t="s">
+        <v>2581</v>
+      </c>
+      <c r="K272" t="s">
+        <v>60</v>
+      </c>
+      <c r="L272" t="s">
+        <v>2582</v>
+      </c>
+      <c r="M272" t="s">
+        <v>62</v>
+      </c>
+      <c r="N272" t="s">
+        <v>2583</v>
+      </c>
+      <c r="O272" t="s">
+        <v>2584</v>
+      </c>
+      <c r="P272" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>66</v>
+      </c>
+      <c r="R272" t="s"/>
+      <c r="S272" t="s">
+        <v>67</v>
+      </c>
+      <c r="T272" t="s">
+        <v>2585</v>
+      </c>
+      <c r="U272" t="s"/>
+      <c r="V272" t="s">
+        <v>2586</v>
+      </c>
+      <c r="W272" t="s"/>
+      <c r="X272" t="s"/>
+      <c r="Y272" t="s"/>
+      <c r="Z272" t="s"/>
+      <c r="AA272" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="273" spans="1:27">
+      <c r="A273" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B273" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C273" t="s"/>
+      <c r="D273" t="s">
+        <v>2432</v>
+      </c>
+      <c r="E273" t="s"/>
+      <c r="F273" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G273" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H273" t="s">
+        <v>2589</v>
+      </c>
+      <c r="I273" t="s">
+        <v>2590</v>
+      </c>
+      <c r="J273" t="s">
+        <v>2591</v>
+      </c>
+      <c r="K273" t="s">
+        <v>60</v>
+      </c>
+      <c r="L273" t="s">
+        <v>2592</v>
+      </c>
+      <c r="M273" t="s">
+        <v>62</v>
+      </c>
+      <c r="N273" t="s">
+        <v>2593</v>
+      </c>
+      <c r="O273" t="s">
+        <v>2594</v>
+      </c>
+      <c r="P273" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>66</v>
+      </c>
+      <c r="R273" t="s"/>
+      <c r="S273" t="s">
+        <v>67</v>
+      </c>
+      <c r="T273" t="s">
+        <v>2595</v>
+      </c>
+      <c r="U273" t="s"/>
+      <c r="V273" t="s">
+        <v>2596</v>
+      </c>
+      <c r="W273" t="s"/>
+      <c r="X273" t="s"/>
+      <c r="Y273" t="s"/>
+      <c r="Z273" t="s"/>
+      <c r="AA273" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" spans="1:27">
+      <c r="A274" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B274" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C274" t="s"/>
+      <c r="D274" t="s">
+        <v>2599</v>
+      </c>
+      <c r="E274" t="s"/>
+      <c r="F274" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G274" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H274" t="s">
+        <v>2600</v>
+      </c>
+      <c r="I274" t="s">
+        <v>2601</v>
+      </c>
+      <c r="J274" t="s">
+        <v>2602</v>
+      </c>
+      <c r="K274" t="s">
+        <v>60</v>
+      </c>
+      <c r="L274" t="s">
+        <v>2603</v>
+      </c>
+      <c r="M274" t="s">
+        <v>62</v>
+      </c>
+      <c r="N274" t="s">
+        <v>2604</v>
+      </c>
+      <c r="O274" t="s">
+        <v>2605</v>
+      </c>
+      <c r="P274" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>66</v>
+      </c>
+      <c r="R274" t="s"/>
+      <c r="S274" t="s">
+        <v>67</v>
+      </c>
+      <c r="T274" t="s">
+        <v>2606</v>
+      </c>
+      <c r="U274" t="s"/>
+      <c r="V274" t="s">
+        <v>2607</v>
+      </c>
+      <c r="W274" t="s"/>
+      <c r="X274" t="s"/>
+      <c r="Y274" t="s"/>
+      <c r="Z274" t="s"/>
+      <c r="AA274" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="275" spans="1:27">
+      <c r="A275" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B275" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C275" t="s"/>
+      <c r="D275" t="s">
+        <v>2608</v>
+      </c>
+      <c r="E275" t="s"/>
+      <c r="F275" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G275" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H275" t="s">
+        <v>2609</v>
+      </c>
+      <c r="I275" t="s">
+        <v>2610</v>
+      </c>
+      <c r="J275" t="s">
+        <v>2611</v>
+      </c>
+      <c r="K275" t="s">
+        <v>60</v>
+      </c>
+      <c r="L275" t="s">
+        <v>2612</v>
+      </c>
+      <c r="M275" t="s">
+        <v>62</v>
+      </c>
+      <c r="N275" t="s">
+        <v>2613</v>
+      </c>
+      <c r="O275" t="s">
+        <v>2614</v>
+      </c>
+      <c r="P275" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>66</v>
+      </c>
+      <c r="R275" t="s"/>
+      <c r="S275" t="s">
+        <v>67</v>
+      </c>
+      <c r="T275" t="s">
+        <v>2615</v>
+      </c>
+      <c r="U275" t="s"/>
+      <c r="V275" t="s">
+        <v>2616</v>
+      </c>
+      <c r="W275" t="s"/>
+      <c r="X275" t="s"/>
+      <c r="Y275" t="s"/>
+      <c r="Z275" t="s"/>
+      <c r="AA275" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="276" spans="1:27">
+      <c r="A276" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B276" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C276" t="s"/>
+      <c r="D276" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E276" t="s"/>
+      <c r="F276" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G276" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H276" t="s">
+        <v>2618</v>
+      </c>
+      <c r="I276" t="s">
+        <v>2619</v>
+      </c>
+      <c r="J276" t="s">
+        <v>2620</v>
+      </c>
+      <c r="K276" t="s">
+        <v>60</v>
+      </c>
+      <c r="L276" t="s">
+        <v>2621</v>
+      </c>
+      <c r="M276" t="s">
+        <v>62</v>
+      </c>
+      <c r="N276" t="s">
+        <v>2622</v>
+      </c>
+      <c r="O276" t="s">
+        <v>2623</v>
+      </c>
+      <c r="P276" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>66</v>
+      </c>
+      <c r="R276" t="s"/>
+      <c r="S276" t="s">
+        <v>67</v>
+      </c>
+      <c r="T276" t="s">
+        <v>2624</v>
+      </c>
+      <c r="U276" t="s"/>
+      <c r="V276" t="s">
+        <v>2625</v>
+      </c>
+      <c r="W276" t="s"/>
+      <c r="X276" t="s"/>
+      <c r="Y276" t="s"/>
+      <c r="Z276" t="s"/>
+      <c r="AA276" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" spans="1:27">
+      <c r="A277" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B277" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C277" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D277" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E277" t="s"/>
+      <c r="F277" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G277" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H277" t="s">
+        <v>2629</v>
+      </c>
+      <c r="I277" t="s">
+        <v>2630</v>
+      </c>
+      <c r="J277" t="s">
+        <v>2631</v>
+      </c>
+      <c r="K277" t="s">
+        <v>60</v>
+      </c>
+      <c r="L277" t="s">
+        <v>2632</v>
+      </c>
+      <c r="M277" t="s">
+        <v>62</v>
+      </c>
+      <c r="N277" t="s">
+        <v>2633</v>
+      </c>
+      <c r="O277" t="s">
+        <v>2634</v>
+      </c>
+      <c r="P277" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>66</v>
+      </c>
+      <c r="R277" t="s"/>
+      <c r="S277" t="s">
+        <v>67</v>
+      </c>
+      <c r="T277" t="s">
+        <v>2635</v>
+      </c>
+      <c r="U277" t="s"/>
+      <c r="V277" t="s">
+        <v>2636</v>
+      </c>
+      <c r="W277" t="s"/>
+      <c r="X277" t="s"/>
+      <c r="Y277" t="s"/>
+      <c r="Z277" t="s"/>
+      <c r="AA277" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:27">
+      <c r="A278" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B278" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D278" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E278" t="s"/>
+      <c r="F278" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G278" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H278" t="s">
+        <v>2640</v>
+      </c>
+      <c r="I278" t="s">
+        <v>2641</v>
+      </c>
+      <c r="J278" t="s">
+        <v>2642</v>
+      </c>
+      <c r="K278" t="s">
+        <v>60</v>
+      </c>
+      <c r="L278" t="s">
+        <v>2643</v>
+      </c>
+      <c r="M278" t="s">
+        <v>62</v>
+      </c>
+      <c r="N278" t="s">
+        <v>2644</v>
+      </c>
+      <c r="O278" t="s">
+        <v>2645</v>
+      </c>
+      <c r="P278" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>66</v>
+      </c>
+      <c r="R278" t="s"/>
+      <c r="S278" t="s">
+        <v>67</v>
+      </c>
+      <c r="T278" t="s">
+        <v>2646</v>
+      </c>
+      <c r="U278" t="s"/>
+      <c r="V278" t="s">
+        <v>2647</v>
+      </c>
+      <c r="W278" t="s"/>
+      <c r="X278" t="s"/>
+      <c r="Y278" t="s"/>
+      <c r="Z278" t="s"/>
+      <c r="AA278" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:27">
+      <c r="A279" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B279" t="s">
+        <v>2649</v>
+      </c>
+      <c r="C279" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D279" t="s">
+        <v>2599</v>
+      </c>
+      <c r="E279" t="s"/>
+      <c r="F279" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G279" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H279" t="s">
+        <v>2650</v>
+      </c>
+      <c r="I279" t="s">
+        <v>2651</v>
+      </c>
+      <c r="J279" t="s">
+        <v>2652</v>
+      </c>
+      <c r="K279" t="s">
+        <v>60</v>
+      </c>
+      <c r="L279" t="s">
+        <v>2653</v>
+      </c>
+      <c r="M279" t="s">
+        <v>62</v>
+      </c>
+      <c r="N279" t="s">
+        <v>2654</v>
+      </c>
+      <c r="O279" t="s">
+        <v>2655</v>
+      </c>
+      <c r="P279" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>66</v>
+      </c>
+      <c r="R279" t="s"/>
+      <c r="S279" t="s">
+        <v>67</v>
+      </c>
+      <c r="T279" t="s">
+        <v>2656</v>
+      </c>
+      <c r="U279" t="s"/>
+      <c r="V279" t="s">
+        <v>2657</v>
+      </c>
+      <c r="W279" t="s"/>
+      <c r="X279" t="s"/>
+      <c r="Y279" t="s"/>
+      <c r="Z279" t="s"/>
+      <c r="AA279" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="280" spans="1:27">
+      <c r="A280" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B280" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C280" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D280" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E280" t="s"/>
+      <c r="F280" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G280" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H280" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I280" t="s">
+        <v>2662</v>
+      </c>
+      <c r="J280" t="s">
+        <v>2663</v>
+      </c>
+      <c r="K280" t="s">
+        <v>60</v>
+      </c>
+      <c r="L280" t="s">
+        <v>2664</v>
+      </c>
+      <c r="M280" t="s">
+        <v>62</v>
+      </c>
+      <c r="N280" t="s">
+        <v>2665</v>
+      </c>
+      <c r="O280" t="s">
+        <v>2666</v>
+      </c>
+      <c r="P280" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>66</v>
+      </c>
+      <c r="R280" t="s"/>
+      <c r="S280" t="s">
+        <v>67</v>
+      </c>
+      <c r="T280" t="s">
+        <v>2667</v>
+      </c>
+      <c r="U280" t="s"/>
+      <c r="V280" t="s">
+        <v>2668</v>
+      </c>
+      <c r="W280" t="s"/>
+      <c r="X280" t="s"/>
+      <c r="Y280" t="s"/>
+      <c r="Z280" t="s"/>
+      <c r="AA280" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="281" spans="1:27">
+      <c r="A281" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B281" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C281" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D281" t="s">
+        <v>2466</v>
+      </c>
+      <c r="E281" t="s"/>
+      <c r="F281" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G281" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H281" t="s">
+        <v>2672</v>
+      </c>
+      <c r="I281" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J281" t="s">
+        <v>2674</v>
+      </c>
+      <c r="K281" t="s">
+        <v>60</v>
+      </c>
+      <c r="L281" t="s">
+        <v>2675</v>
+      </c>
+      <c r="M281" t="s">
+        <v>62</v>
+      </c>
+      <c r="N281" t="s">
+        <v>2676</v>
+      </c>
+      <c r="O281" t="s">
+        <v>2677</v>
+      </c>
+      <c r="P281" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>66</v>
+      </c>
+      <c r="R281" t="s"/>
+      <c r="S281" t="s">
+        <v>67</v>
+      </c>
+      <c r="T281" t="s">
+        <v>2678</v>
+      </c>
+      <c r="U281" t="s"/>
+      <c r="V281" t="s">
+        <v>2679</v>
+      </c>
+      <c r="W281" t="s"/>
+      <c r="X281" t="s"/>
+      <c r="Y281" t="s"/>
+      <c r="Z281" t="s"/>
+      <c r="AA281" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:27">
+      <c r="A282" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B282" t="s">
+        <v>2649</v>
+      </c>
+      <c r="C282" t="s">
+        <v>2681</v>
+      </c>
+      <c r="D282" t="s">
+        <v>2682</v>
+      </c>
+      <c r="E282" t="s"/>
+      <c r="F282" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G282" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H282" t="s">
+        <v>2683</v>
+      </c>
+      <c r="I282" t="s">
+        <v>2684</v>
+      </c>
+      <c r="J282" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K282" t="s">
+        <v>60</v>
+      </c>
+      <c r="L282" t="s">
+        <v>2686</v>
+      </c>
+      <c r="M282" t="s">
+        <v>62</v>
+      </c>
+      <c r="N282" t="s">
+        <v>2687</v>
+      </c>
+      <c r="O282" t="s">
+        <v>2688</v>
+      </c>
+      <c r="P282" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>66</v>
+      </c>
+      <c r="R282" t="s"/>
+      <c r="S282" t="s">
+        <v>67</v>
+      </c>
+      <c r="T282" t="s">
+        <v>2689</v>
+      </c>
+      <c r="U282" t="s"/>
+      <c r="V282" t="s">
+        <v>2690</v>
+      </c>
+      <c r="W282" t="s"/>
+      <c r="X282" t="s"/>
+      <c r="Y282" t="s"/>
+      <c r="Z282" t="s"/>
+      <c r="AA282" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:27">
+      <c r="A283" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B283" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C283" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D283" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E283" t="s"/>
+      <c r="F283" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G283" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H283" t="s">
+        <v>2693</v>
+      </c>
+      <c r="I283" t="s">
+        <v>2694</v>
+      </c>
+      <c r="J283" t="s">
+        <v>2695</v>
+      </c>
+      <c r="K283" t="s">
+        <v>60</v>
+      </c>
+      <c r="L283" t="s">
+        <v>2696</v>
+      </c>
+      <c r="M283" t="s">
+        <v>62</v>
+      </c>
+      <c r="N283" t="s">
+        <v>2697</v>
+      </c>
+      <c r="O283" t="s">
+        <v>2698</v>
+      </c>
+      <c r="P283" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>66</v>
+      </c>
+      <c r="R283" t="s"/>
+      <c r="S283" t="s">
+        <v>67</v>
+      </c>
+      <c r="T283" t="s">
+        <v>2699</v>
+      </c>
+      <c r="U283" t="s"/>
+      <c r="V283" t="s">
+        <v>2700</v>
+      </c>
+      <c r="W283" t="s"/>
+      <c r="X283" t="s"/>
+      <c r="Y283" t="s"/>
+      <c r="Z283" t="s"/>
+      <c r="AA283" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:27">
+      <c r="A284" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B284" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D284" t="s">
+        <v>2702</v>
+      </c>
+      <c r="E284" t="s"/>
+      <c r="F284" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G284" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H284" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I284" t="s">
+        <v>2704</v>
+      </c>
+      <c r="J284" t="s">
+        <v>2705</v>
+      </c>
+      <c r="K284" t="s">
+        <v>60</v>
+      </c>
+      <c r="L284" t="s">
+        <v>2706</v>
+      </c>
+      <c r="M284" t="s">
+        <v>62</v>
+      </c>
+      <c r="N284" t="s">
+        <v>2707</v>
+      </c>
+      <c r="O284" t="s">
+        <v>2708</v>
+      </c>
+      <c r="P284" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>66</v>
+      </c>
+      <c r="R284" t="s"/>
+      <c r="S284" t="s">
+        <v>67</v>
+      </c>
+      <c r="T284" t="s">
+        <v>2709</v>
+      </c>
+      <c r="U284" t="s"/>
+      <c r="V284" t="s">
+        <v>2710</v>
+      </c>
+      <c r="W284" t="s"/>
+      <c r="X284" t="s"/>
+      <c r="Y284" t="s"/>
+      <c r="Z284" t="s"/>
+      <c r="AA284" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:27">
+      <c r="A285" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B285" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D285" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E285" t="s"/>
+      <c r="F285" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G285" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H285" t="s">
+        <v>2712</v>
+      </c>
+      <c r="I285" t="s">
+        <v>2713</v>
+      </c>
+      <c r="J285" t="s">
+        <v>2714</v>
+      </c>
+      <c r="K285" t="s">
+        <v>60</v>
+      </c>
+      <c r="L285" t="s">
+        <v>2715</v>
+      </c>
+      <c r="M285" t="s">
+        <v>62</v>
+      </c>
+      <c r="N285" t="s">
+        <v>2716</v>
+      </c>
+      <c r="O285" t="s">
+        <v>2717</v>
+      </c>
+      <c r="P285" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>66</v>
+      </c>
+      <c r="R285" t="s"/>
+      <c r="S285" t="s">
+        <v>67</v>
+      </c>
+      <c r="T285" t="s">
+        <v>2718</v>
+      </c>
+      <c r="U285" t="s"/>
+      <c r="V285" t="s">
+        <v>2719</v>
+      </c>
+      <c r="W285" t="s"/>
+      <c r="X285" t="s"/>
+      <c r="Y285" t="s"/>
+      <c r="Z285" t="s"/>
+      <c r="AA285" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:27">
+      <c r="A286" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B286" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2720</v>
+      </c>
+      <c r="D286" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E286" t="s"/>
+      <c r="F286" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G286" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H286" t="s">
+        <v>2721</v>
+      </c>
+      <c r="I286" t="s">
+        <v>2722</v>
+      </c>
+      <c r="J286" t="s">
+        <v>2723</v>
+      </c>
+      <c r="K286" t="s">
+        <v>60</v>
+      </c>
+      <c r="L286" t="s">
+        <v>2724</v>
+      </c>
+      <c r="M286" t="s">
+        <v>62</v>
+      </c>
+      <c r="N286" t="s">
+        <v>2725</v>
+      </c>
+      <c r="O286" t="s">
+        <v>2726</v>
+      </c>
+      <c r="P286" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>66</v>
+      </c>
+      <c r="R286" t="s"/>
+      <c r="S286" t="s">
+        <v>67</v>
+      </c>
+      <c r="T286" t="s">
+        <v>2727</v>
+      </c>
+      <c r="U286" t="s"/>
+      <c r="V286" t="s">
+        <v>2728</v>
+      </c>
+      <c r="W286" t="s"/>
+      <c r="X286" t="s"/>
+      <c r="Y286" t="s"/>
+      <c r="Z286" t="s"/>
+      <c r="AA286" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:27">
+      <c r="A287" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B287" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D287" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E287" t="s"/>
+      <c r="F287" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G287" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H287" t="s">
+        <v>2732</v>
+      </c>
+      <c r="I287" t="s">
+        <v>2733</v>
+      </c>
+      <c r="J287" t="s">
+        <v>2734</v>
+      </c>
+      <c r="K287" t="s">
+        <v>60</v>
+      </c>
+      <c r="L287" t="s">
+        <v>2735</v>
+      </c>
+      <c r="M287" t="s">
+        <v>62</v>
+      </c>
+      <c r="N287" t="s">
+        <v>2736</v>
+      </c>
+      <c r="O287" t="s">
+        <v>2737</v>
+      </c>
+      <c r="P287" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>66</v>
+      </c>
+      <c r="R287" t="s"/>
+      <c r="S287" t="s">
+        <v>67</v>
+      </c>
+      <c r="T287" t="s">
+        <v>2738</v>
+      </c>
+      <c r="U287" t="s"/>
+      <c r="V287" t="s">
+        <v>2739</v>
+      </c>
+      <c r="W287" t="s"/>
+      <c r="X287" t="s"/>
+      <c r="Y287" t="s"/>
+      <c r="Z287" t="s"/>
+      <c r="AA287" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:27">
+      <c r="A288" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B288" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D288" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E288" t="s"/>
+      <c r="F288" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G288" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H288" t="s">
+        <v>2744</v>
+      </c>
+      <c r="I288" t="s">
+        <v>2745</v>
+      </c>
+      <c r="J288" t="s">
+        <v>2746</v>
+      </c>
+      <c r="K288" t="s">
+        <v>60</v>
+      </c>
+      <c r="L288" t="s">
+        <v>2747</v>
+      </c>
+      <c r="M288" t="s">
+        <v>62</v>
+      </c>
+      <c r="N288" t="s">
+        <v>2748</v>
+      </c>
+      <c r="O288" t="s">
+        <v>2749</v>
+      </c>
+      <c r="P288" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>66</v>
+      </c>
+      <c r="R288" t="s"/>
+      <c r="S288" t="s">
+        <v>67</v>
+      </c>
+      <c r="T288" t="s">
+        <v>2750</v>
+      </c>
+      <c r="U288" t="s"/>
+      <c r="V288" t="s">
+        <v>2751</v>
+      </c>
+      <c r="W288" t="s"/>
+      <c r="X288" t="s"/>
+      <c r="Y288" t="s"/>
+      <c r="Z288" t="s"/>
+      <c r="AA288" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="289" spans="1:27">
+      <c r="A289" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B289" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2754</v>
+      </c>
+      <c r="D289" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E289" t="s"/>
+      <c r="F289" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G289" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H289" t="s">
+        <v>2756</v>
+      </c>
+      <c r="I289" t="s">
+        <v>2757</v>
+      </c>
+      <c r="J289" t="s">
+        <v>2758</v>
+      </c>
+      <c r="K289" t="s">
+        <v>60</v>
+      </c>
+      <c r="L289" t="s">
+        <v>2759</v>
+      </c>
+      <c r="M289" t="s">
+        <v>62</v>
+      </c>
+      <c r="N289" t="s">
+        <v>2760</v>
+      </c>
+      <c r="O289" t="s">
+        <v>2761</v>
+      </c>
+      <c r="P289" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>66</v>
+      </c>
+      <c r="R289" t="s"/>
+      <c r="S289" t="s">
+        <v>67</v>
+      </c>
+      <c r="T289" t="s">
+        <v>2762</v>
+      </c>
+      <c r="U289" t="s"/>
+      <c r="V289" t="s">
+        <v>2763</v>
+      </c>
+      <c r="W289" t="s"/>
+      <c r="X289" t="s"/>
+      <c r="Y289" t="s"/>
+      <c r="Z289" t="s"/>
+      <c r="AA289" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:27">
+      <c r="A290" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B290" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C290" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D290" t="s">
+        <v>2766</v>
+      </c>
+      <c r="E290" t="s"/>
+      <c r="F290" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G290" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H290" t="s">
+        <v>2767</v>
+      </c>
+      <c r="I290" t="s">
+        <v>2768</v>
+      </c>
+      <c r="J290" t="s">
+        <v>2769</v>
+      </c>
+      <c r="K290" t="s">
+        <v>60</v>
+      </c>
+      <c r="L290" t="s">
+        <v>2770</v>
+      </c>
+      <c r="M290" t="s">
+        <v>62</v>
+      </c>
+      <c r="N290" t="s">
+        <v>2771</v>
+      </c>
+      <c r="O290" t="s">
+        <v>2772</v>
+      </c>
+      <c r="P290" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>66</v>
+      </c>
+      <c r="R290" t="s"/>
+      <c r="S290" t="s">
+        <v>67</v>
+      </c>
+      <c r="T290" t="s">
+        <v>2773</v>
+      </c>
+      <c r="U290" t="s"/>
+      <c r="V290" t="s">
+        <v>2774</v>
+      </c>
+      <c r="W290" t="s"/>
+      <c r="X290" t="s"/>
+      <c r="Y290" t="s"/>
+      <c r="Z290" t="s"/>
+      <c r="AA290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:27">
+      <c r="A291" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B291" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D291" t="s">
+        <v>2778</v>
+      </c>
+      <c r="E291" t="s"/>
+      <c r="F291" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G291" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H291" t="s">
+        <v>2779</v>
+      </c>
+      <c r="I291" t="s">
+        <v>2780</v>
+      </c>
+      <c r="J291" t="s">
+        <v>2781</v>
+      </c>
+      <c r="K291" t="s">
+        <v>60</v>
+      </c>
+      <c r="L291" t="s">
+        <v>2782</v>
+      </c>
+      <c r="M291" t="s">
+        <v>62</v>
+      </c>
+      <c r="N291" t="s">
+        <v>2783</v>
+      </c>
+      <c r="O291" t="s">
+        <v>2784</v>
+      </c>
+      <c r="P291" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>66</v>
+      </c>
+      <c r="R291" t="s"/>
+      <c r="S291" t="s">
+        <v>67</v>
+      </c>
+      <c r="T291" t="s">
+        <v>2785</v>
+      </c>
+      <c r="U291" t="s"/>
+      <c r="V291" t="s">
+        <v>2786</v>
+      </c>
+      <c r="W291" t="s"/>
+      <c r="X291" t="s"/>
+      <c r="Y291" t="s"/>
+      <c r="Z291" t="s"/>
+      <c r="AA291" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292" spans="1:27">
+      <c r="A292" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B292" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C292" t="s"/>
+      <c r="D292" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E292" t="s"/>
+      <c r="F292" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G292" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H292" t="s">
+        <v>2789</v>
+      </c>
+      <c r="I292" t="s">
+        <v>2790</v>
+      </c>
+      <c r="J292" t="s">
+        <v>2791</v>
+      </c>
+      <c r="K292" t="s">
+        <v>60</v>
+      </c>
+      <c r="L292" t="s">
+        <v>2792</v>
+      </c>
+      <c r="M292" t="s">
+        <v>62</v>
+      </c>
+      <c r="N292" t="s">
+        <v>2793</v>
+      </c>
+      <c r="O292" t="s">
+        <v>2794</v>
+      </c>
+      <c r="P292" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>66</v>
+      </c>
+      <c r="R292" t="s"/>
+      <c r="S292" t="s">
+        <v>67</v>
+      </c>
+      <c r="T292" t="s">
+        <v>2795</v>
+      </c>
+      <c r="U292" t="s"/>
+      <c r="V292" t="s">
+        <v>2796</v>
+      </c>
+      <c r="W292" t="s"/>
+      <c r="X292" t="s"/>
+      <c r="Y292" t="s"/>
+      <c r="Z292" t="s"/>
+      <c r="AA292" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:27">
+      <c r="A293" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B293" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C293" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D293" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E293" t="s"/>
+      <c r="F293" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G293" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H293" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I293" t="s">
+        <v>2802</v>
+      </c>
+      <c r="J293" t="s">
+        <v>2803</v>
+      </c>
+      <c r="K293" t="s">
+        <v>60</v>
+      </c>
+      <c r="L293" t="s">
+        <v>2804</v>
+      </c>
+      <c r="M293" t="s">
+        <v>62</v>
+      </c>
+      <c r="N293" t="s">
+        <v>2805</v>
+      </c>
+      <c r="O293" t="s">
+        <v>2806</v>
+      </c>
+      <c r="P293" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>66</v>
+      </c>
+      <c r="R293" t="s"/>
+      <c r="S293" t="s">
+        <v>67</v>
+      </c>
+      <c r="T293" t="s">
+        <v>2807</v>
+      </c>
+      <c r="U293" t="s"/>
+      <c r="V293" t="s">
+        <v>2808</v>
+      </c>
+      <c r="W293" t="s"/>
+      <c r="X293" t="s"/>
+      <c r="Y293" t="s"/>
+      <c r="Z293" t="s"/>
+      <c r="AA293" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="294" spans="1:27">
+      <c r="A294" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B294" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C294" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D294" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E294" t="s"/>
+      <c r="F294" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G294" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H294" t="s">
+        <v>2812</v>
+      </c>
+      <c r="I294" t="s">
+        <v>2813</v>
+      </c>
+      <c r="J294" t="s">
+        <v>2814</v>
+      </c>
+      <c r="K294" t="s">
+        <v>60</v>
+      </c>
+      <c r="L294" t="s">
+        <v>2815</v>
+      </c>
+      <c r="M294" t="s">
+        <v>62</v>
+      </c>
+      <c r="N294" t="s">
+        <v>2816</v>
+      </c>
+      <c r="O294" t="s">
+        <v>2817</v>
+      </c>
+      <c r="P294" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>66</v>
+      </c>
+      <c r="R294" t="s"/>
+      <c r="S294" t="s">
+        <v>67</v>
+      </c>
+      <c r="T294" t="s">
+        <v>2818</v>
+      </c>
+      <c r="U294" t="s"/>
+      <c r="V294" t="s">
+        <v>2819</v>
+      </c>
+      <c r="W294" t="s"/>
+      <c r="X294" t="s"/>
+      <c r="Y294" t="s"/>
+      <c r="Z294" t="s"/>
+      <c r="AA294" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="295" spans="1:27">
+      <c r="A295" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B295" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D295" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E295" t="s"/>
+      <c r="F295" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G295" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H295" t="s">
+        <v>2824</v>
+      </c>
+      <c r="I295" t="s">
+        <v>2825</v>
+      </c>
+      <c r="J295" t="s">
+        <v>2826</v>
+      </c>
+      <c r="K295" t="s">
+        <v>60</v>
+      </c>
+      <c r="L295" t="s">
+        <v>2827</v>
+      </c>
+      <c r="M295" t="s">
+        <v>62</v>
+      </c>
+      <c r="N295" t="s">
+        <v>2828</v>
+      </c>
+      <c r="O295" t="s">
+        <v>2829</v>
+      </c>
+      <c r="P295" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>66</v>
+      </c>
+      <c r="R295" t="s"/>
+      <c r="S295" t="s">
+        <v>67</v>
+      </c>
+      <c r="T295" t="s">
+        <v>2830</v>
+      </c>
+      <c r="U295" t="s"/>
+      <c r="V295" t="s">
+        <v>2831</v>
+      </c>
+      <c r="W295" t="s"/>
+      <c r="X295" t="s"/>
+      <c r="Y295" t="s"/>
+      <c r="Z295" t="s"/>
+      <c r="AA295" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:27">
+      <c r="A296" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B296" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D296" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E296" t="s"/>
+      <c r="F296" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G296" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H296" t="s">
+        <v>2835</v>
+      </c>
+      <c r="I296" t="s">
+        <v>2836</v>
+      </c>
+      <c r="J296" t="s">
+        <v>2837</v>
+      </c>
+      <c r="K296" t="s">
+        <v>60</v>
+      </c>
+      <c r="L296" t="s">
+        <v>2838</v>
+      </c>
+      <c r="M296" t="s">
+        <v>62</v>
+      </c>
+      <c r="N296" t="s">
+        <v>2839</v>
+      </c>
+      <c r="O296" t="s">
+        <v>2840</v>
+      </c>
+      <c r="P296" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>66</v>
+      </c>
+      <c r="R296" t="s"/>
+      <c r="S296" t="s">
+        <v>67</v>
+      </c>
+      <c r="T296" t="s">
+        <v>2841</v>
+      </c>
+      <c r="U296" t="s"/>
+      <c r="V296" t="s">
+        <v>2842</v>
+      </c>
+      <c r="W296" t="s"/>
+      <c r="X296" t="s"/>
+      <c r="Y296" t="s"/>
+      <c r="Z296" t="s"/>
+      <c r="AA296" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" spans="1:27">
+      <c r="A297" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B297" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D297" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E297" t="s"/>
+      <c r="F297" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G297" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H297" t="s">
+        <v>2847</v>
+      </c>
+      <c r="I297" t="s">
+        <v>2848</v>
+      </c>
+      <c r="J297" t="s">
+        <v>2849</v>
+      </c>
+      <c r="K297" t="s">
+        <v>60</v>
+      </c>
+      <c r="L297" t="s">
+        <v>2850</v>
+      </c>
+      <c r="M297" t="s">
+        <v>62</v>
+      </c>
+      <c r="N297" t="s">
+        <v>2851</v>
+      </c>
+      <c r="O297" t="s">
+        <v>2852</v>
+      </c>
+      <c r="P297" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>66</v>
+      </c>
+      <c r="R297" t="s"/>
+      <c r="S297" t="s">
+        <v>67</v>
+      </c>
+      <c r="T297" t="s">
+        <v>2853</v>
+      </c>
+      <c r="U297" t="s"/>
+      <c r="V297" t="s">
+        <v>2854</v>
+      </c>
+      <c r="W297" t="s"/>
+      <c r="X297" t="s"/>
+      <c r="Y297" t="s"/>
+      <c r="Z297" t="s"/>
+      <c r="AA297" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="298" spans="1:27">
+      <c r="A298" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B298" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D298" t="s">
+        <v>2857</v>
+      </c>
+      <c r="E298" t="s"/>
+      <c r="F298" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G298" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H298" t="s">
+        <v>2858</v>
+      </c>
+      <c r="I298" t="s">
+        <v>2859</v>
+      </c>
+      <c r="J298" t="s">
+        <v>2860</v>
+      </c>
+      <c r="K298" t="s">
+        <v>60</v>
+      </c>
+      <c r="L298" t="s">
+        <v>2861</v>
+      </c>
+      <c r="M298" t="s">
+        <v>62</v>
+      </c>
+      <c r="N298" t="s">
+        <v>2862</v>
+      </c>
+      <c r="O298" t="s">
+        <v>2863</v>
+      </c>
+      <c r="P298" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>66</v>
+      </c>
+      <c r="R298" t="s"/>
+      <c r="S298" t="s">
+        <v>67</v>
+      </c>
+      <c r="T298" t="s">
+        <v>2864</v>
+      </c>
+      <c r="U298" t="s"/>
+      <c r="V298" t="s">
+        <v>2865</v>
+      </c>
+      <c r="W298" t="s"/>
+      <c r="X298" t="s"/>
+      <c r="Y298" t="s"/>
+      <c r="Z298" t="s"/>
+      <c r="AA298" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="299" spans="1:27">
+      <c r="A299" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B299" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D299" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E299" t="s"/>
+      <c r="F299" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G299" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H299" t="s">
+        <v>2867</v>
+      </c>
+      <c r="I299" t="s">
+        <v>2868</v>
+      </c>
+      <c r="J299" t="s">
+        <v>2869</v>
+      </c>
+      <c r="K299" t="s">
+        <v>60</v>
+      </c>
+      <c r="L299" t="s">
+        <v>2870</v>
+      </c>
+      <c r="M299" t="s">
+        <v>62</v>
+      </c>
+      <c r="N299" t="s">
+        <v>2871</v>
+      </c>
+      <c r="O299" t="s">
+        <v>2872</v>
+      </c>
+      <c r="P299" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>66</v>
+      </c>
+      <c r="R299" t="s"/>
+      <c r="S299" t="s">
+        <v>67</v>
+      </c>
+      <c r="T299" t="s">
+        <v>2873</v>
+      </c>
+      <c r="U299" t="s"/>
+      <c r="V299" t="s">
+        <v>2874</v>
+      </c>
+      <c r="W299" t="s"/>
+      <c r="X299" t="s"/>
+      <c r="Y299" t="s"/>
+      <c r="Z299" t="s"/>
+      <c r="AA299" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="300" spans="1:27">
+      <c r="A300" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B300" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2877</v>
+      </c>
+      <c r="D300" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E300" t="s"/>
+      <c r="F300" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G300" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H300" t="s">
+        <v>2879</v>
+      </c>
+      <c r="I300" t="s">
+        <v>2880</v>
+      </c>
+      <c r="J300" t="s">
+        <v>2881</v>
+      </c>
+      <c r="K300" t="s">
+        <v>60</v>
+      </c>
+      <c r="L300" t="s">
+        <v>2882</v>
+      </c>
+      <c r="M300" t="s">
+        <v>62</v>
+      </c>
+      <c r="N300" t="s">
+        <v>2883</v>
+      </c>
+      <c r="O300" t="s">
+        <v>2884</v>
+      </c>
+      <c r="P300" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q300" t="s">
+        <v>66</v>
+      </c>
+      <c r="R300" t="s"/>
+      <c r="S300" t="s">
+        <v>67</v>
+      </c>
+      <c r="T300" t="s">
+        <v>2885</v>
+      </c>
+      <c r="U300" t="s"/>
+      <c r="V300" t="s">
+        <v>2886</v>
+      </c>
+      <c r="W300" t="s"/>
+      <c r="X300" t="s"/>
+      <c r="Y300" t="s"/>
+      <c r="Z300" t="s"/>
+      <c r="AA300" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="301" spans="1:27">
+      <c r="A301" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B301" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D301" t="s">
+        <v>2889</v>
+      </c>
+      <c r="E301" t="s"/>
+      <c r="F301" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G301" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H301" t="s">
+        <v>2890</v>
+      </c>
+      <c r="I301" t="s">
+        <v>2891</v>
+      </c>
+      <c r="J301" t="s">
+        <v>2892</v>
+      </c>
+      <c r="K301" t="s">
+        <v>60</v>
+      </c>
+      <c r="L301" t="s">
+        <v>2893</v>
+      </c>
+      <c r="M301" t="s">
+        <v>62</v>
+      </c>
+      <c r="N301" t="s">
+        <v>2894</v>
+      </c>
+      <c r="O301" t="s">
+        <v>2895</v>
+      </c>
+      <c r="P301" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q301" t="s">
+        <v>66</v>
+      </c>
+      <c r="R301" t="s"/>
+      <c r="S301" t="s">
+        <v>67</v>
+      </c>
+      <c r="T301" t="s">
+        <v>2896</v>
+      </c>
+      <c r="U301" t="s"/>
+      <c r="V301" t="s">
+        <v>2897</v>
+      </c>
+      <c r="W301" t="s"/>
+      <c r="X301" t="s"/>
+      <c r="Y301" t="s"/>
+      <c r="Z301" t="s"/>
+      <c r="AA301" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="302" spans="1:27">
+      <c r="A302" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B302" t="s">
+        <v>2876</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D302" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E302" t="s"/>
+      <c r="F302" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G302" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H302" t="s">
+        <v>2901</v>
+      </c>
+      <c r="I302" t="s">
+        <v>2902</v>
+      </c>
+      <c r="J302" t="s">
+        <v>2903</v>
+      </c>
+      <c r="K302" t="s">
+        <v>60</v>
+      </c>
+      <c r="L302" t="s">
+        <v>2904</v>
+      </c>
+      <c r="M302" t="s">
+        <v>62</v>
+      </c>
+      <c r="N302" t="s">
+        <v>2905</v>
+      </c>
+      <c r="O302" t="s">
+        <v>2906</v>
+      </c>
+      <c r="P302" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q302" t="s">
+        <v>66</v>
+      </c>
+      <c r="R302" t="s"/>
+      <c r="S302" t="s">
+        <v>67</v>
+      </c>
+      <c r="T302" t="s">
+        <v>2907</v>
+      </c>
+      <c r="U302" t="s"/>
+      <c r="V302" t="s">
+        <v>2908</v>
+      </c>
+      <c r="W302" t="s"/>
+      <c r="X302" t="s"/>
+      <c r="Y302" t="s"/>
+      <c r="Z302" t="s"/>
+      <c r="AA302" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="303" spans="1:27">
+      <c r="A303" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B303" t="s">
+        <v>2910</v>
+      </c>
+      <c r="C303" t="s"/>
+      <c r="D303" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E303" t="s"/>
+      <c r="F303" t="s">
+        <v>2479</v>
+      </c>
+      <c r="G303" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H303" t="s">
+        <v>2912</v>
+      </c>
+      <c r="I303" t="s">
+        <v>2913</v>
+      </c>
+      <c r="J303" t="s">
+        <v>2914</v>
+      </c>
+      <c r="K303" t="s">
+        <v>60</v>
+      </c>
+      <c r="L303" t="s">
+        <v>2915</v>
+      </c>
+      <c r="M303" t="s">
+        <v>62</v>
+      </c>
+      <c r="N303" t="s">
+        <v>2916</v>
+      </c>
+      <c r="O303" t="s">
+        <v>2917</v>
+      </c>
+      <c r="P303" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q303" t="s">
+        <v>66</v>
+      </c>
+      <c r="R303" t="s"/>
+      <c r="S303" t="s">
+        <v>67</v>
+      </c>
+      <c r="T303" t="s">
+        <v>2918</v>
+      </c>
+      <c r="U303" t="s"/>
+      <c r="V303" t="s">
+        <v>2919</v>
+      </c>
+      <c r="W303" t="s"/>
+      <c r="X303" t="s"/>
+      <c r="Y303" t="s"/>
+      <c r="Z303" t="s"/>
+      <c r="AA303" t="n">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/docs/collections/kanok/metadata/data.xlsx
+++ b/docs/collections/kanok/metadata/data.xlsx
@@ -7430,7 +7430,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/kanok/document/186f660c-38cd-4aa1-31f8-288b1d6d1a80</t>
   </si>
   <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/05801d0cc8c5351a2dc27b214fac259bce655c91.jpg</t>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/52dc3234099fe8440eefff15b9c4df50907ab855.jpg</t>
   </si>
   <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1167353</t>
@@ -26633,7 +26633,7 @@
       <c r="Y261" t="s"/>
       <c r="Z261" t="s"/>
       <c r="AA261" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:27">
@@ -26702,7 +26702,7 @@
       <c r="Y262" t="s"/>
       <c r="Z262" t="s"/>
       <c r="AA262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263" spans="1:27">
